--- a/untitled folder/HSC_Physics_2nd_Paper_Chapter_01_Thermodynamics.xlsx
+++ b/untitled folder/HSC_Physics_2nd_Paper_Chapter_01_Thermodynamics.xlsx
@@ -1168,11 +1168,6 @@
           <t>তাপগতিবিদ্যার শূন্যতম সূত্রটি বিবৃত করো এবং দেখাও যে কীভাবে এটি তাপমাত্রাকে একটি বস্তুনিষ্ঠ তাপগতীয় অবস্থা অপেক্ষক (state function) হিসেবে সংজ্ঞায়িত করে। কেন এই সূত্রটিকে প্রথম ও দ্বিতীয় সূত্রের নামকরণের অনেক পরে আবিষ্কার হওয়া সত্ত্বেও 'শূন্যতম সূত্র' নাম দেওয়া হয়েছিল?</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>শূন্যতম সূত্রের সমতুল্যতা সম্পর্ক ও নামকরণের ইতিহাস:</t>
@@ -1218,11 +1213,6 @@
           <t>একটি প্ল্যাটিনাম রোধ থার্মোমিটারে প্ল্যাটিনাম তারের রোধ হিমাঙ্কে ($0^\circ\text{C}$) $R_0 = 10.00\text{ }\Omega$, স্ফুটনাঙ্কে ($100^\circ\text{C}$) $R_{100} = 13.90\text{ }\Omega$ এবং একটি অজ্ঞাত তরলের ফুটন্ত অবস্থায় $R_t = 15.85\text{ }\Omega$ পাওয়া গেল। ক্যালেন্ডারের রৈখিক রোধ সূত্রানুসারে তরলটির তাপমাত্রা সেলসিয়াস স্কেলে নির্ণয় করো। উচ্চ তাপমাত্রায় ক্যালেন্ডার-ভ্যান ডুসেন সমীকরণ $R_t = R_0[1 + A t + B t^2]$ ব্যবহারের প্রয়োজনীয়তা কী?</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>প্ল্যাটিনাম রোধ থার্মোমিটারে তাপমাত্রা নির্ণয় ও দ্বিঘাত সংশোধন:</t>
@@ -1268,11 +1258,6 @@
           <t>একটি স্থির আয়তন গ্যাস থার্মোমিটারে আদর্শ গ্যাসের চাপ পানির ত্রৈধ বিন্দুতে ($273.16\text{ K}$) $P_{\text{tr}} = 80.0\text{ kPa}$ এবং একটি অজানা চুল্লির তাপে $P = 140.0\text{ kPa}$ পাওয়া গেল। চুল্লিটির তাপমাত্রা কেলভিন স্কেলে কত? কেন আধুনিক আন্তর্জাতিক পরিমাপ পদ্ধতিতে দুটি স্থির বিন্দুর (হিমাঙ্ক ও স্ফুটনাঙ্ক) বদলে পানির ত্রৈধ বিন্দুকে একক মৌলিক প্রমাণ বিন্দু হিসেবে গ্রহণ করা হয়েছে?</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>স্থির আয়তন গ্যাস থার্মোমিটার ও ত্রৈধ বিন্দুর অনন্যতা:</t>
@@ -1318,11 +1303,6 @@
           <t>একটি থার্মোকাপলে কপার-কনস্ট্যান্টান সংযোগের তাপ-তড়িৎচালক বল $E = a t + b t^2$ সমীকরণ মেনে চলে, যেখানে $t$ হলো তপ্ত সংযোগের সেলসিয়াস তাপমাত্রা (শীতল সংযোগ $0^\circ\text{C}$-এ রক্ষিত)। যদি নিরপেক্ষ তাপমাত্রা (neutral temperature) $t_n = 280^\circ\text{C}$ হয়, তবে পরিবর্তন তাপমাত্রা (temperature of inversion $t_i$) কত হবে? নিরপেক্ষ তাপমাত্রায় সিবেক সহগ (Seebeck coefficient $S = dE/dt$)-এর মান কত?</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>থার্মোকাপলের নিরপেক্ষ ও পরিবর্তন তাপমাত্রা বিশ্লেষণ:</t>
@@ -1368,11 +1348,6 @@
           <t>দুটি ভিন্ন উপাদানের থার্মোমিটার (যেমন পারদ থার্মোমিটার এবং স্থির আয়তন হাইড্রোজেন গ্যাস থার্মোমিটার) $0^\circ\text{C}$ এবং $100^\circ\text{C}$ স্থির বিন্দুতে নিখুঁতভাবে একমত হলেও মধ্যবর্তী কোনো তাপমাত্রা যেমন $50^\circ\text{C}$-এ তাদের পাঠের মধ্যে সামান্য বিচ্যুতি দেখা যায় কেন? পরম তাপগতীয় তাপমাত্রা স্কেলের (Kelvin absolute scale) শ্রেষ্ঠত্ব ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>থার্মোমেট্রিক পদার্থের সীমাবদ্ধতা বনাম কেলভিনের পরম স্কেল:</t>
@@ -1418,11 +1393,6 @@
           <t>অপটিক্যাল পাইরোমিটার (Optical Pyrometer) কোন নীতির ওপর ভিত্তি করে অতি উচ্চ তাপমাত্রা পরিমাপ করে? স্টিফান-বোল্টজম্যান সূত্র এবং ভিনের সরণ সূত্রের সাহায্যে ব্যাখ্যা করো কেন স্পর্শহীন বিকিরণ থার্মোমিটার সূর্য বা গলিত ইস্পাতের তাপমাত্রা পরিমাপে একমাত্র কার্যকর পদ্ধতি।</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>পাইরোমেট্রি ও কৃষ্ণবস্তু বিকিরণ সূত্রের প্রয়োগ:</t>
@@ -1468,11 +1438,6 @@
           <t>একটি ত্রুটিপূর্ণ থার্মোমিটার গলিত বরফে $-2^\circ$ পাঠ দেয় এবং প্রমাণ চাপে ফুটন্ত পানিতে $103^\circ$ পাঠ দেয়। থার্মোমিটারটি যখন $40^\circ$ পাঠ প্রদর্শন করে, তখন সেলসিয়াস স্কেলে প্রকৃত তাপমাত্রা কত? কোন তাপমাত্রায় ত্রুটিপূর্ণ থার্মোমিটারের পাঠ এবং ফারেনহাইট স্কেলের পাঠের সাংখ্যিক মান একই হবে?</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>ত্রুটিপূর্ণ থার্মোমিটারের রূপান্তর ও ফারেনহাইট সমতা নির্ণয়:</t>
@@ -1518,11 +1483,6 @@
           <t>কোয়ান্টাম স্পিন সিস্টেমে বা লেজার পদার্থবিদ্যায় 'পরম ঋণাত্মক তাপমাত্রা' (Absolute Negative Temperature, $-T$) বলতে কী বোঝায়? বোল্টজম্যানের এনট্রপি সংজ্ঞা $\frac{1}{T} = \left(\frac{\partial S}{\partial E}\right)$ ব্যবহার করে দেখাও যে ঋণাত্মক তাপমাত্রার একটি ব্যবস্থা যেকোনো ধনাত্মক পরম তাপমাত্রার ব্যবস্থার চেয়েও বেশি উত্তপ্ত!</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>পপুলেশন ইনভার্সন ও ঋণাত্মক কেলভিন তাপমাত্রার প্যারাডক্স:</t>
@@ -1568,11 +1528,6 @@
           <t>একটি বিশেষ গ্যাসীয় থার্মোমিটারে তাপমাত্রার স্কেল $T = A \ln(P) + B$ সূত্র মেনে চলে। পানির ত্রৈধ বিন্দুতে ($273.16\text{ K}$) চাপ $P = 1.5\text{ atm}$ এবং সীসার গলনাঙ্কে ($600.6\text{ K}$) চাপ $P = 7.5\text{ atm}$। ধ্রুবক $A$ ও $B$-এর মান নির্ণয় করো এবং $P = 3.0\text{ atm}$ চাপে তাপমাত্রা কত হবে গণনা করো। [$\ln 2 = 0.693, \ln 5 = 1.609$]</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>লগারিদমিক তাপমাত্রিক স্কেলের ধ্রুবক ও পাঠ নির্ণয়:</t>
@@ -1618,11 +1573,6 @@
           <t>কোয়ার্টজ ক্রিস্টাল থার্মোমিটারে পিজোইলেকট্রিক রেজোন্যান্স কম্পাঙ্কের তাপমাত্রা সহগ কীভাবে কাজ করে? কেন এটি ডিজিটাল তাপমাত্রামাপক হিসেবে আধুনিক গবেষণাগারে মিলিকেলভিন ($\text{mK}$) স্তরের সূক্ষ্মতা প্রদানে আদর্শ?</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>কোয়ার্টজ রেজোন্যান্স থার্মোমেট্রির সূক্ষ্মতা ও আধুনিক প্রয়োগ:</t>
@@ -1668,11 +1618,6 @@
           <t>তাপগতিবিদ্যার প্রথম সূত্রটি গাণিতিকভাবে উপস্থাপন করো এবং দেখাও যে কেন তাপ $\delta Q$ এবং কাজ $\delta W$ পথ-নির্ভর (অপূর্ণ ব্যবকলক / inexact differential) হলেও অভ্যন্তরীণ শক্তির পরিবর্তন $dU = \delta Q - \delta W$ একটি পথ-স্বাধীন অবস্থা অপেক্ষক (পূর্ণ ব্যবকলক / exact differential)। সাইক্লিক প্রক্রিয়ায় প্রথম সূত্রের রূপ কী?</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>প্রথম সূত্রের গাণিতিক রূপ ও অবস্থা অপেক্ষকের প্রমাণ:</t>
@@ -1718,11 +1663,6 @@
           <t>একটি আদর্শ গ্যাসের $n\text{ mol}$ পরিমাণকে সমোষ্ণ প্রক্রিয়ায় আদি আয়তন $V_1$ থেকে চূড়ান্ত আয়তন $V_2$-তে প্রসারিত করা হলো। গ্যাস কর্তৃক সম্পাদিত কাজের রাশিমালা $W_{\text{iso}} = n R T \ln\left(\frac{V_2}{V_1}\right) = n R T \ln\left(\frac{P_1}{P_2}\right)$ প্রতিপাদন করো। প্রক্রিয়ায় গ্যাসটির অভ্যন্তরীণ শক্তির পরিবর্তন $\Delta U$ এবং শোষিত তাপ $Q$-এর মান কত?</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>সমোষ্ণ প্রসারণের কাজ ও প্রথম সূত্রের বিশ্লেষণ:</t>
@@ -1768,11 +1708,6 @@
           <t>একটি আদর্শ গ্যাস $P-V$ চিত্রে একটি উপবৃত্তাকার চক্র (elliptical cycle) সম্পন্ন করে যার সমীকরণ $\frac{(P - P_0)^2}{a^2} + \frac{(V - V_0)^2}{b^2} = 1$। চক্রটি ঘড়ির কাঁটার দিকে আবর্তিত হলে প্রতি চক্রে গ্যাস কর্তৃক সম্পাদিত নেট কাজ কত? চক্রটিতে প্রতি চক্রে গ্যাস দ্বারা শোষিত নেট তাপ কত?</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>উপবৃত্তাকার তাপগতীয় চক্রে নেট কৃতকাজ নির্ণয়:</t>
@@ -1818,11 +1753,6 @@
           <t>গে-লুসাক-জুল মুক্ত প্রসারণ (free expansion into vacuum) কী? একটি গ্যাসকে তাপনিরোধক পাত্রে বায়ুশূন্য স্থানে প্রসারিত হতে দিলে কেন $W = 0$ এবং $Q = 0$ হয়? এটি ব্যবহার করে কীভাবে প্রমাণ করা যায় যে আদর্শ গ্যাসের অভ্যন্তরীণ শক্তি কেবল তাপমাত্রার ওপর নির্ভর করে, আয়তন বা চাপের ওপর নয়?</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>মুক্ত প্রসারণ ও আদর্শ গ্যাসের জুলের নীতি প্রমাণ:</t>
@@ -1919,11 +1849,6 @@
           <t>একটি আবদ্ধ সিলিন্ডারে $n = 1\text{ mol}$ হিলিয়াম গ্যাস ($C_v = \frac{3}{2}R$) $T_1 = 300\text{ K}$ তাপমাত্রা থেকে উত্তপ্ত হয়ে $T_2 = 600\text{ K}$-এ পৌঁছায় এমন একটি প্রক্রিয়ায় যেখানে চাপ ও আয়তনের সম্পর্ক $P = \alpha V$ (যেখানে $\alpha$ একটি ধ্রুবক)। (i) গ্যাস কর্তৃক সম্পাদিত কাজ, (ii) অভ্যন্তরীণ শক্তির পরিবর্তন, এবং (iii) গ্যাসটির মোলার তাপধারণ ক্ষমতা নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>সরলরৈখিক প্রক্রিয়ার কৃতকাজ ও মোলার তাপধারণ ক্ষমতা গণনা:</t>
@@ -1969,11 +1894,6 @@
           <t>একটি তরল সাবান ফিল্মের পৃষ্ঠের ক্ষেত্রফল $A$ থেকে বৃদ্ধি করে $A + \Delta A$ করতে কৃতকাজের রাশিমালা $dW = -2\gamma dA$ প্রতিপাদন করো, যেখানে $\gamma$ হলো পৃষ্ঠটান। সাবান ফিল্মের দ্রুত রুদ্ধতাপীয় প্রসারণে ফিল্মটির তাপমাত্রা কেন হ্রাস পায় তা প্রথম সূত্রের সাহায্যে ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>পৃষ্ঠটানের তাপগতীয় কাজ ও পৃষ্ঠ প্রসারণে শীতলীকরণ:</t>
@@ -2019,11 +1939,6 @@
           <t>চুম্বকীয় পদার্থে তাপগতিবিদ্যার প্রথম সূত্রের রূপ $dQ = dU - \mu_0 H dM$ উপস্থাপন করো। রুদ্ধতাপীয় বিচুম্বকায়ন (Adiabatic Demagnetization) প্রক্রিয়ায় কীভাবে শক্তিশালী চৌম্বক ক্ষেত্র হঠাৎ অপসারণ করে মিলিকেলভিন ও মাইক্রোকেলভিন পরম তাপমাত্রায় পৌঁছানো সম্ভব হয়?</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>চৌম্বক তাপগতিবিদ্যা ও রুদ্ধতাপীয় বিচুম্বকায়নে অতি-শীতলীকরণ:</t>
@@ -2069,11 +1984,6 @@
           <t>একটি ত্রিভুজাকার চক্রে $P-V$ তলে তিনটি পর্যায় রয়েছে: (i) $A \to B$ সমচাপ প্রসারণ ($P_1, V_1 \to P_1, V_2$), (ii) $B \to C$ সমআয়তন চাপ হ্রাস ($P_1, V_2 \to P_2, V_2$), এবং (iii) $C \to A$ সরলরৈখিক পথ বরাবর প্রাথমিক অবস্থায় প্রত্যাবর্তন। চক্রটিতে প্রতি চক্রে গ্যাস কর্তৃক সম্পাদিত নেট কাজের মান জ্যামিতিক পদ্ধতিতে নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>ত্রিভুজাকার তাপগতীয় চক্রের নেট কাজ প্রতিপাদন:</t>
@@ -2119,11 +2029,6 @@
           <t>একটি আদর্শ গ্যাসের অবস্থার সমীকরণ $PV = nRT$ হলেও বাস্তব গ্যাসের ক্ষেত্রে প্রথম সূত্রে অভ্যন্তরীণ শক্তি কেন আয়তনের ওপরও নির্ভরশীল হয়? ভ্যান ডার ওয়ালস গ্যাসের জন্য সমোষ্ণ প্রসারণে কৃতকাজ $W = n R T \ln\left(\frac{V_2 - nb}{V_1 - nb}\right)$ প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>ভ্যান ডার ওয়ালস গ্যাসের সমোষ্ণ কাজ প্রতিপাদন:</t>
@@ -2169,11 +2074,6 @@
           <t>প্রত্যাবর্তী রুদ্ধতাপীয় প্রক্রিয়ায় আদর্শ গ্যাসের জন্য $P V^\gamma = \text{ধ্রুবক}$, $T V^{\gamma - 1} = \text{ধ্রুবক}$, এবং $T^\gamma P^{1 - \gamma} = \text{ধ্রুবক}$ সমীকরণ তিনটি প্রথম সূত্র থেকে নিখুঁতভাবে প্রতিপাদন করো। $P-V$ চিত্রে রুদ্ধতাপীয় বক্ররেখার ঢাল সমোষ্ণ বক্ররেখার ঢালের কত গুণ?</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>রুদ্ধতাপীয় সমীকরণমালা প্রতিপাদন ও ঢালের সম্পর্ক:</t>
@@ -2219,11 +2119,6 @@
           <t>একটি আদর্শ গ্যাসের রুদ্ধতাপীয় প্রসারণে গ্যাস কর্তৃক সম্পাদিত কাজের সমীকরণ $W_{\text{adia}} = \frac{P_1 V_1 - P_2 V_2}{\gamma - 1} = \frac{n R (T_1 - T_2)}{\gamma - 1} = -\Delta U$ প্রতিপাদন করো। গ্যাসটি প্রসারিত হলে তাপমাত্রা হ্রাস পায় কেন?</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>রুদ্ধতাপীয় কাজের প্রতিপাদন ও তাপমাত্রা হ্রাসের ভৌত কারণ:</t>
@@ -2269,11 +2164,6 @@
           <t>পলিট্রপিক প্রক্রিয়া (Polytropic process $P V^n = \text{ধ্রুবক}$) কী? দেখাও যে একটি পলিট্রপিক প্রক্রিয়ায় গ্যাসের মোলার তাপধারণ ক্ষমতা $C = C_v + \frac{R}{1 - n}$। কোন শর্তে পলিট্রপিক মোলার তাপধারণ ক্ষমতা ঋণাত্মক ($C &lt; 0$) হয় এবং ঋণাত্মক তাপধারণ ক্ষমতার ভৌত অর্থ কী?</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>পলিট্রপিক তাপধারণ ক্ষমতা ও ঋণাত্মক তাপ ধারণের তাৎপর্য:</t>
@@ -2319,11 +2209,6 @@
           <t>পলিট্রপিক সূচক $n$-এর বিভিন্ন বিশেষ মানের জন্য প্রক্রিয়াসমূহ শনাক্ত করো: (i) $n = 0$, (ii) $n = 1$, (iii) $n = \gamma$, এবং (iv) $n \to \pm \infty$। প্রতিটি ক্ষেত্রে তাপধারণ ক্ষমতার মান কত?</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>পলিট্রপিক সূচকের বিশেষ মানসমূহের সার্বিক সারণি:</t>
@@ -2369,11 +2254,6 @@
           <t>একটি আদর্শ দ্বি-পরমাণুক গ্যাসকে ($\gamma = 1.4$) প্রাথমিক অবস্থা ($P_1 = 1\text{ atm}, T_1 = 300\text{ K}$) থেকে রুদ্ধতাপীয়ভাবে তার আদি আয়তনের এক-চতুর্থাংশে ($V_2 = V_1/4$) সংকুচিত করা হলো। গ্যাসটির চূড়ান্ত চাপ $P_2$ এবং চূড়ান্ত তাপমাত্রা $T_2$ কত হবে? গ্যাসটির প্রতি মোলে কৃতকাজের মান নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>দ্বি-পরমাণুক গ্যাসের রুদ্ধতাপীয় সংকোচনের হিসাব:</t>
@@ -2419,11 +2299,6 @@
           <t>একই প্রাথমিক অবস্থা ($P_0, V_0$) থেকে একটি আদর্শ গ্যাসকে সমান চূড়ান্ত আয়তন $2V_0$-তে প্রসারিত করা হলো: (ক) সমোষ্ণ প্রক্রিয়ায়, এবং (খ) রুদ্ধতাপীয় প্রক্রিয়ায়। কোন প্রক্রিয়ায় গ্যাস কর্তৃক সম্পাদিত কাজ বেশি হবে এবং কোন প্রক্রিয়ায় চূড়ান্ত চাপ বেশি হবে? $P-V$ লেখচিত্রের সাহায্যে ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>সমোষ্ণ বনাম রুদ্ধতাপীয় প্রসারণের কাজ ও চাপের তুলনা:</t>
@@ -2469,11 +2344,6 @@
           <t>প্রশ্ন ২৬-এর উল্টো ক্ষেত্রে, গ্যাসটিকে আদি আয়তন $V_0$ থেকে সংকুচিত করে অর্ধেক ($V_0/2$) করা হলো: (ক) সমোষ্ণভাবে, এবং (খ) রুদ্ধতাপীয়ভাবে। কোন ক্ষেত্রে গ্যাসের ওপর বেশি কাজ করতে হবে এবং কেন?</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>সমোষ্ণ বনাম রুদ্ধতাপীয় সংকোচনে কাজের তুলনা:</t>
@@ -2519,11 +2389,6 @@
           <t>একটি ডিজেল ইঞ্জিনে বাতাসকে প্রাথমিক অবস্থা ($1\text{ atm}, 300\text{ K}$) থেকে রুদ্ধতাপীয়ভাবে তার আদি আয়তনের এক-বিংশতিমাংশে ($V_2 = V_1/20$, সংকোচন অনুপাত $r = 20$) সংকুচিত করা হয়। বাতাসের তাপমাত্রা কত বৃদ্ধি পাবে? ডিজেল ইঞ্জিনে কেন কোনো স্পার্ক প্লাগের প্রয়োজন হয় না? [$\gamma = 1.4$]</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>ডিজেল ইঞ্জিনের স্বতঃস্ফূর্ত প্রজ্বলন ও সংকোচন অনুপাত:</t>
@@ -2569,11 +2434,6 @@
           <t>একটি আদর্শ এক-পরমাণুক গ্যাস ($\gamma = 5/3$) এমন একটি পলিট্রপিক প্রক্রিয়া অনুসরণ করে যেখানে $P \propto T^3$। পলিট্রপিক সূচক $n$ এবং প্রক্রিয়াটিতে গ্যাসের মোলার তাপধারণ ক্ষমতা $C$ নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>তাপমাত্রা-চাপ সম্পর্ক থেকে পলিট্রপিক সূচক ও তাপধারণ ক্ষমতা নির্ণয়:</t>
@@ -2619,11 +2479,6 @@
           <t>একটি শব্দ তরঙ্গের বাতাসের মধ্য দিয়ে সঞ্চালনকে ল্যাপলাস কেন একটি দ্রুত রুদ্ধতাপীয় প্রক্রিয়া হিসেবে বিবেচনা করেছিলেন? শব্দ তরঙ্গের ক্ষেত্রে রুদ্ধতাপীয় বাল্ক মডুলাস $B_{\text{adia}} = \gamma P$ প্রতিপাদন করো এবং দেখাও যে সমোষ্ণ বাল্ক মডুলাসের তুলনায় এটি $\gamma$ গুণ বৃহত্তর।</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>শব্দ তরঙ্গে রুদ্ধতাপীয় বাল্ক মডুলাসের প্রতিপাদন:</t>
@@ -2669,11 +2524,6 @@
           <t>তাপগতিবিদ্যার দ্বিতীয় সূত্রের কেলভিন-প্ল্যাঙ্ক বিবৃতি এবং ক্লসিয়াস বিবৃতি উল্লেখ করো। লজিক্যাল ডিডাকশনের মাধ্যমে প্রমাণ করো যে এই দুটি বিবৃতি পরস্পরের সম্পূর্ণ সমতুল্য (অর্থাৎ একটি লঙ্ঘিত হলে অপরটিও লঙ্ঘিত হয়)। দ্বিতীয় প্রকার অবিরত গতিযন্ত্র (PMM-2) কেন অসম্ভব?</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>দ্বিতীয় সূত্রের দুই বিবৃতির সমতুল্যতা প্রমাণ ও PMM-2:</t>
@@ -2770,11 +2620,6 @@
           <t>কার্নোর উপপাদ্য (Carnot's Theorem) বিবৃত করো এবং প্রমাণ করো যে: (i) নির্দিষ্ট দুটি তাপমাত্রার মধ্যে কার্যরত কোনো অপ্রত্যাবর্তী ইঞ্জিনের দক্ষতা প্রত্যাবর্তী কার্নো ইঞ্জিনের চেয়ে বেশি হতে পারে না ($\eta_{\text{irr}} \le \eta_{\text{rev}}$), এবং (ii) একই দুটি তাপমাত্রার মধ্যে কার্যরত সকল প্রত্যাবর্তী ইঞ্জিনের দক্ষতা সমান, তাদের কার্যকরী পদার্থ যাই হোক না কেন।</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>কার্নো উপপাদ্যের দ্বিমুখী প্রমাণ:</t>
@@ -2820,11 +2665,6 @@
           <t>একটি কার্নো ইঞ্জিন $T_1 = 500\text{ K}$ এবং $T_2 = 300\text{ K}$ তাপমাত্রার আধারের মধ্যে কাজ করে প্রতি চক্রে $W = 1000\text{ J}$ কাজ সম্পাদন করে। (i) ইঞ্জিনটির দক্ষতা, (ii) প্রতি চক্রে উৎস থেকে শোষিত তাপ $Q_1$, এবং (iii) গ্রাহকে বর্জিত তাপ $Q_2$ নির্ণয় করো। ইঞ্জিনটির দক্ষতা $50\%$ করতে হলে উৎসের তাপমাত্রা কত বৃদ্ধি করতে হবে?</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>কার্নো ইঞ্জিনের দক্ষতা, তাপ শোষণ ও তাপমাত্রা বৃদ্ধি গণনা:</t>
@@ -2870,11 +2710,6 @@
           <t>দুটি কার্নো ইঞ্জিন শ্রেণিবদ্ধভাবে (in series) সংযুক্ত আছে। প্রথম ইঞ্জিনটি $T_1$ তাপমাত্রা থেকে তাপ গ্রহণ করে $T$ তাপমাত্রায় তাপ বর্জন করে। দ্বিতীয় ইঞ্জিনটি এই বর্জিত তাপ গ্রহণ করে $T_2$ তাপমাত্রার গ্রাহকে তাপ বর্জন করে। অন্তর্বর্তী তাপমাত্রা $T$-এর মান নির্ণয় করো যখন: (ক) উভয় ইঞ্জিনের সম্পাদিত কাজের পরিমাণ সমান হয় ($W_1 = W_2$), এবং (খ) উভয় ইঞ্জিনের দক্ষতা সমান হয় ($\eta_1 = \eta_2$)।</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>শ্রেণিবদ্ধ কার্নো ইঞ্জিনের অন্তর্বর্তী তাপমাত্রা প্রতিপাদন:</t>
@@ -2920,11 +2755,6 @@
           <t>পেট্রল ইঞ্জিনের চার-স্ট্রোক অটো চক্রের (Otto cycle) তাপগতীয় ধাপসমূহ $P-V$ চিত্রে দেখাও এবং প্রমাণ করো যে অটো ইঞ্জিনের তাত্ত্বিক দক্ষতা $\eta = 1 - \frac{1}{r^{\gamma - 1}}$, যেখানে $r = V_1 / V_2$ হলো সংকোচন অনুপাত। বাস্তব অটো ইঞ্জিনে সংকোচন অনুপাত সাধারণত ৮ থেকে ১০-এর বেশি বাড়ানো যায় না কেন (ইঞ্জিন নকিং)?</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>অটো চক্রের দক্ষতা প্রতিপাদন ও নকিং সীমাবদ্ধতা:</t>
@@ -2970,11 +2800,6 @@
           <t>স্টার্লিং চক্র (Stirling cycle) কী? দুটি সমোষ্ণ এবং দুটি স্থির আয়তন প্রক্রিয়ার সমন্বয়ে গঠিত এই চক্রে কীভাবে রিজেনারেটর (regenerator) ব্যবহারের মাধ্যমে কার্নো ইঞ্জিনের সমান তাত্ত্বিক দক্ষতা $\eta = 1 - T_L/T_H$ অর্জন করা সম্ভব হয়?</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>স্টার্লিং চক্রের রিজেনারেশন নীতি ও কার্নো দক্ষতা সমতুল্যতা:</t>
@@ -3020,11 +2845,6 @@
           <t>সীমাবদ্ধ সময়ের তাপগতিবিদ্যায় কার্জন-আলবর্ন দক্ষতা (Curzon-Ahlborn efficiency) $\eta_{\text{CA}} = 1 - \sqrt{\frac{T_L}{T_H}}$ বলতে কী বোঝায়? একটি আদর্শ কার্নো ইঞ্জিন কেন শূন্য ক্ষমতা (zero power output) প্রদান করে এবং বাস্তব বিদ্যুৎ কেন্দ্রসমূহের দক্ষতা কেন কার্নো দক্ষতার চেয়ে কার্জন-আলবর্ন দক্ষতার অনেক কাছাকাছি থাকে?</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>কার্জন-আলবর্ন সর্বাধিক ক্ষমতা দক্ষতা বনাম কার্নো দক্ষতার প্যারাডক্স:</t>
@@ -3070,11 +2890,6 @@
           <t>একটি উদ্ভাবক দাবি করলেন যে তিনি এমন একটি তাপ ইঞ্জিন আবিষ্কার করেছেন যা $T_1 = 600\text{ K}$ উৎস থেকে $Q_1 = 1000\text{ J}$ তাপ গ্রহণ করে $W = 600\text{ J}$ যান্ত্রিক কাজ সম্পন্ন করে এবং $T_2 = 300\text{ K}$ গ্রাহকে $Q_2 = 400\text{ J}$ তাপ বর্জন করে। তাপগতিবিদ্যার প্রথম ও দ্বিতীয় সূত্রের নিরিখে উদ্ভাবকের দাবির সত্যতা যাচাই করো।</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>ইঞ্জিনের দাবির প্রথম ও দ্বিতীয় সূত্রীয় সত্যতা যাচাই:</t>
@@ -3120,11 +2935,6 @@
           <t>একটি দ্বি-পরমাণুক আদর্শ গ্যাস ব্যবহারকারী কার্নো ইঞ্জিনের সমোষ্ণ প্রসারণে আয়তন দ্বিগুণ হয় ($V_B = 2V_A$) এবং পরবর্তী রুদ্ধতাপীয় প্রসারণে আয়তন পুনরায় দ্বিগুণ হয় ($V_C = 2V_B$)। ইঞ্জিনটির কর্মদক্ষতা কত? [$\gamma = 1.4$]</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>আয়তন অনুপাত থেকে কার্নো ইঞ্জিনের দক্ষতা গণনা:</t>
@@ -3170,11 +2980,6 @@
           <t>বিপরীতমুখী কার্নো চক্রে পরিচালিত একটি রেফ্রিজারেটরের কর্মক্ষমতা গুণক (Coefficient of Performance, $COP_{\text{ref}}$ বা $\beta$) এবং একটি হিট পাম্পের কর্মক্ষমতা গুণকের ($COP_{\text{HP}}$ বা $\gamma$) রাশিমালা প্রতিপাদন করো। প্রমাণ করো যে একই তাপমাত্রার পাল্লায় $COP_{\text{HP}} = COP_{\text{ref}} + 1$। হিট পাম্পের $COP$ কেন সর্বদা একের চেয়ে বড় হয়?</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>রেফ্রিজারেটর ও হিট পাম্পের সিওপি প্রতিপাদন ও সম্পর্ক:</t>
@@ -3220,11 +3025,6 @@
           <t>একটি সুষম তাপনিরোধক বন্ধ ঘরের ভেতরে চালু অবস্থায় থাকা একটি রেফ্রিজারেটরের দরজা খোলা রেখে দিলে ঘরের ভেতরের তাপমাত্রা হ্রাস পাবে, বৃদ্ধি পাবে, নাকি অপরিবর্তিত থাকবে? তাপগতিবিদ্যার প্রথম ও দ্বিতীয় সূত্রের ভিত্তিতে বিস্তারিত ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>খোলা দরজাযুক্ত রেফ্রিজারেটরে ঘরের তাপমাত্রা বৃদ্ধির কারণ:</t>
@@ -3270,11 +3070,6 @@
           <t>একটি কার্নো রেফ্রিজারেটর $T_L = -10^\circ\text{C}$ তাপমাত্রা থেকে তাপ শোষণ করে $T_H = 27^\circ\text{C}$ তাপমাত্রার ঘরে তাপ বর্জন করে। (i) রেফ্রিজারেটরটির কর্মক্ষমতা গুণক ($COP$) কত? (ii) বরফ বানানোর জন্য রেফ্রিজারেটরটিকে যদি $0^\circ\text{C}$-এর $m = 2\text{ kg}$ পানিকে $0^\circ\text{C}$-এর বরফে রূপান্তর করতে হয়, তবে কম্প্রেসার দ্বারা ন্যূনতম কত যান্ত্রিক কাজ সম্পন্ন করতে হবে? [বরফ গলনের সুপ্ততাপ $L_f = 3.36 \times 10^5\text{ J kg}^{-1}$]</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>কার্নো রেফ্রিজারেটরের সিওপি ও পানি বরফ করার কাজ গণনা:</t>
@@ -3320,11 +3115,6 @@
           <t>শীতপ্রধান দেশে একটি বাড়ি গরম রাখতে সরাসরি বৈদ্যুতিক রোধ হিটার (electric resistance heater) ব্যবহারের চেয়ে একটি ইলেকট্রিক হিট পাম্প ব্যবহার করা কেন প্রায় ৩ থেকে ৪ গুণ বেশি সাশ্রয়ী? $COP = 3.5$ বিশিষ্ট একটি হিট পাম্পের বিদ্যুৎ খরচ ও তাপ সরবরাহের তুলনা করো।</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>হিট পাম্প বনাম রেজিস্ট্যান্স হিটারের জ্বালানি সাশ্রয়িতা:</t>
@@ -3370,11 +3160,6 @@
           <t>একটি আদর্শ কার্নো ইঞ্জিন এবং একটি কার্নো রেফ্রিজারেটর একই তাপমাত্রা পাল্লায় ($T_H$ এবং $T_L$) পরিচালিত হয়। প্রমাণ করো যে ইঞ্জিনের দক্ষতা $\eta$ এবং রেফ্রিজারেটরের কর্মক্ষমতা গুণক $\beta$-এর মধ্যে সম্পর্ক $\beta = \frac{1 - \eta}{\eta}$ এবং $\eta = \frac{1}{\beta + 1}$।</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>কার্নো দক্ষতা ও রেফ্রিজারেটর সিওপির পারস্পরিক সম্পর্ক প্রতিপাদন:</t>
@@ -3420,11 +3205,6 @@
           <t>বাষ্প শোষণ রেফ্রিজারেশন ব্যবস্থা (Vapor Absorption Refrigeration System, VARS) কীভাবে কোনো যান্ত্রিক কম্প্রেসার ছাড়াই কাজ করে? অ্যামোনিয়া-পানি বা লিথিয়াম ব্রোমাইড-পানি সিস্টেমে তাপীয় শক্তির (যেমন সৌর তাপ বা শিল্প বর্জ্য তাপ) সরাসরি ব্যবহার করে শীতলীকরণ প্রক্রিয়া ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>বাষ্প শোষণ রেফ্রিজারেশন ও কম্প্রেসারহীন শীতলীকরণ নীতি:</t>
@@ -3470,11 +3250,6 @@
           <t>পেলটিয়ার প্রভাব (Peltier effect) কী এবং থার্মোইলেকট্রিক কুলার (Peltier cooler) কীভাবে কোনো তরল রেফ্রিজারেন্ট বা গতিশীল অংশ ছাড়াই শীতলীকরণ সম্পাদন করে? কম্পিউটার সিপিইউ কুলিং এবং পোর্টেবল ইনসুলিন কুলারে এর উপযোগিতা ও সীমাবদ্ধতা আলোচনা করো।</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>পেলটিয়ার থার্মোইলেকট্রিক কুলিং ও ন্যানো-প্রযুক্তির সুবিধা:</t>
@@ -3520,11 +3295,6 @@
           <t>একটি আবাসিক রেফ্রিজারেটরের গড় বৈদ্যুতিক ক্ষমতা $P = 150\text{ W}$ এবং এটি প্রতিদিন গড়ে এক-তৃতীয়াংশ সময় (duty cycle $33.3\%$) চলে। যদি রেফ্রিজারেটরটির কার্যকর $COP = 2.5$ হয়, তবে এটি প্রতিদিন খাদ্য প্রকোষ্ঠ থেকে কত মেগাজুল ($MJ$) তাপ অপসারণ করে? প্রতি ইউনিট বিদ্যুতের দাম ৭ টাকা হলে প্রতি মাসে বিদ্যুৎ খরচ কত?</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>আবাসিক রেফ্রিজারেটরের তাপ অপসারণ ও মাসিক বিদ্যুৎ বিল গণনা:</t>
@@ -3570,11 +3340,6 @@
           <t>একটি আদর্শ কার্নো ইঞ্জিন দ্বারা চালিত একটি আদর্শ কার্নো হিট পাম্প বিবেচনা করো। ইঞ্জিনটি $T_1$ এবং $T_2$ আধারের মধ্যে কাজ করে যে যান্ত্রিক কাজ উৎপন্ন করে, তা দিয়ে সরাসরি একটি হিট পাম্প পরিচালিত হয় যা $T_3$ পরিবেশ থেকে তাপ গ্রহণ করে $T_2$ ঘরে তাপ সরবরাহ করে। ঘরে মোট প্রাপ্ত তাপ এবং ইঞ্জিনের উৎস থেকে শোষিত তাপের অনুপাত নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>কার্নো ইঞ্জিন-চালিত হিট পাম্পের সামগ্রিক তাপ বিবর্ধন:</t>
@@ -3655,7 +3420,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>কার্নো চক্র ও সর্বোচ্চ কর্মদক্ষতা (সমস্যা 1)</t>
+          <t>তাপগতিবিদ্যার ১ম সূত্র ও তাপগতীয় প্রক্রিয়াসমূহ (1st Law &amp; Processes)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3664,35 +3429,29 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>##PRESET:carnot-cycle[size:medium]##
-[সমস্যা 1: কার্নো চক্র ও সর্বোচ্চ কর্মদক্ষতা]
-##PRESET:carnot-cycle[size:medium]##
-একটি কার্নো ইঞ্জিন $T_1 = 400\text{ K}$ তাপমাত্রার তাপ উৎস হতে $Q_1 = 3000\text{ J}$ তাপ গ্রহণ করে এবং $T_2 = 300\text{ K}$ তাপমাত্রার গ্রাহকে তাপ বর্জন করে। ইঞ্জিনটির কর্মদক্ষতা ($\ eta = 1 - T_2/T_1$) এবং প্রতি চক্রে সম্পাদিত কাজের মান কত?</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি সিস্টেমকে $A$ অবস্থা হতে $B$ অবস্থায় নিতে $80\text{ J}$ তাপ সরবরাহ করা হলো এবং সিস্টেম দ্বারা $30\text{ J}$ কাজ সম্পাদিত হলো। সিস্টেমটিকে অন্য একটি পথে $B$ হতে $A$-তে ফিরিয়ে আনতে সিস্টেমের ওপর $20\text{ J}$ কাজ করা হলে এই প্রত্যাবর্তী প্রক্রিয়ায় কত তাপ বর্জিত হবে?</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>##PRESET:carnot-cycle[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 1)।</t>
+          <t>১ম পথে: $\Delta U = Q - W = 80 - 30 = 50.0\text{ J} = U_B - U_A$। প্রত্যাবর্তী পথে অভ্যন্তরীণ শক্তি পরিবর্তন $\Delta U' = U_A - U_B = -50.0\text{ J}$। সিস্টেমের ওপর কাজ হওয়ায় $W' = -20\text{ J}$। তাপগতিবিদ্যার ১ম সূত্র: $Q' = \Delta U' + W' = -50 + (-20) = -70.0\text{ J}$। অতএব $70.0\text{ J}$ তাপ বর্জিত হবে।</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>বর্জিত তাপ $Q_{B \to A} = -70.0\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3712,12 +3471,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>বরফ গলন ও তাপমাত্রা বৃদ্ধিতে এন্ট্রপি (সমস্যা 2)</t>
+          <t>তাপগতিবিদ্যার ১ম সূত্র ও তাপগতীয় প্রক্রিয়াসমূহ (1st Law &amp; Processes)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -3725,25 +3484,25 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[সমস্যা 2: বরফ গলন ও তাপমাত্রা বৃদ্ধিতে এন্ট্রপি]
-$0^\circ\text{C}$ তাপমাত্রার $60\text{ g}$ বরফকে $50^\circ\text{C}$ তাপমাত্রার পানিতে রূপান্তরিত করা হলো। এই সামগ্রিক প্রক্রিয়ায় মোট এন্ট্রপির পরিবর্তন ($\Delta S$) কত জুল/কেলভিন? ($L_f = 3.36 \times 10^5\text{ J/kg}, s = 4200\text{ J/(kg}\cdot\text{K)}$)</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি আদর্শ গ্যাসের $2.0\text{ মোল}$ গ্যাসকে সমোষ্ণ প্রক্রিয়ায় $300\text{ K}$ স্থির তাপমাত্রায় আদি আয়তন $V_1 = 0.01\text{ m}^3$ হতে সংকুচিত করে $V_2 = 0.002\text{ m}^3$ করা হলো। গ্যাসটির ওপর কৃতকাজ $W$, অভ্যন্তরীণ শক্তির পরিবর্তন $\Delta U$ এবং পরিবেশে নির্গত তাপ $Q$ নির্ণয় কর। ($R = 8.314\text{ J/mol}\cdot\text{K}$)।</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 2)।</t>
+          <t>সমোষ্ণ প্রক্রিয়ায় তাপমাত্রা স্থির থাকায় অভ্যন্তরীণ শক্তির পরিবর্তন $\Delta U = 0$। কৃতকাজ $W = nRT \ln(V_2/V_1) = 2.0 \times 8.314 \times 300 \times \ln(0.002/0.01) = 4988.4 \times \ln(0.2) = 4988.4 \times (-1.60944) \approx -8028.5\text{ J}$। প্রথম সূত্র: $Q = \Delta U + W = 0 + (-8028.5) = -8028.5\text{ J}$।</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>কৃতকাজ $W = -8028.5\text{ J}$, $\Delta U = 0$, নির্গত তাপ $Q = -8028.5\text{ J}$ (পরিবেশে প্রায় $8.03\text{ kJ}$ তাপ নির্গত হয়)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3763,7 +3522,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>রূদ্ধতাপীয় প্রসারণ ও কাজের হিসাব (সমস্যা 3)</t>
+          <t>তাপগতিবিদ্যার ১ম সূত্র ও তাপগতীয় প্রক্রিয়াসমূহ (1st Law &amp; Processes)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3772,35 +3531,29 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>##PRESET:heat-engine[size:medium]##
-[সমস্যা 3: রূদ্ধতাপীয় প্রসারণ ও কাজের হিসাব]
-##PRESET:heat-engine[size:medium]##
-$1\text{ mol}$ হিলিয়াম গ্যাস ($C_v = 1.5R$) প্রারম্ভিক তাপমাত্রা $T_1 = 800\text{ K}$ হতে রূদ্ধতাপীয় প্রক্রিয়ায় প্রসারিত হয়ে তাপমাত্রা $T_2 = 700\text{ K}$-এ নেমে এলো। গ্যাস কর্তৃক সম্পাদিত কাজের মান $W = n C_v(T_1 - T_2)$ কত জুল? ($R = 8.314\text{ J/(mol}\cdot\text{K)}$)</t>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##
+একটি দ্বিপরমাণুক আদর্শ গ্যাসের ($\gamma = 1.40$) প্রাথমিক চাপ $1.0\text{ atm}$ এবং তাপমাত্রা $27^\circ\text{C}$। গ্যাসটিকে রুদ্ধতাপীয় প্রক্রিয়ায় হঠাৎ সংকুচিত করে আয়তন আদি আয়তনের এক-অষ্টমাংশ ($V/8$) করা হলো। অন্তিম চাপ $P_2$ এবং অন্তিম তাপমাত্রা $T_2$ কত হবে?</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>##PRESET:heat-engine[size:medium]##</t>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 3)।</t>
+          <t>রুদ্ধতাপীয় সম্পর্কে: $P_1 V_1^\gamma = P_2 V_2^\gamma \implies P_2 = P_1 (V_1/V_2)^\gamma = 1.0 \times (8)^{1.4} = 8^{7/5} = (2^3)^{1.4} = 2^{4.2} \approx 18.379\text{ atm}$। তাপমাত্রার ক্ষেত্রে: $T_1 V_1^{\gamma-1} = T_2 V_2^{\gamma-1} \implies T_2 = T_1 (V_1/V_2)^{\gamma-1} = 300 \times (8)^{0.4} = 300 \times 2^{1.2} \approx 300 \times 2.2974 = 689.22\text{ K}$। সেলসিয়াসে $\theta_2 = 689.22 - 273 = 416.2^\circ\text{C}$।</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 3</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>অন্তিম চাপ $P_2 = 18.38\text{ atm}$, অন্তিম তাপমাত্রা $T_2 = 689.2\text{ K} = 416.2^\circ\text{C}$</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3820,12 +3573,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>রেফ্রিজারেটরের কার্যসম্পাদন গুণক (COP) (সমস্যা 4)</t>
+          <t>তাপগতিবিদ্যার ১ম সূত্র ও তাপগতীয় প্রক্রিয়াসমূহ (1st Law &amp; Processes)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -3833,25 +3586,25 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>[সমস্যা 4: রেফ্রিজারেটরের কার্যসম্পাদন গুণক (COP)]
-একটি আদর্শ রেফ্রিজারেটর $T_2 = -10^\circ\text{C}$ তাপমাত্রা হতে তাপ শোষণ করে $T_1 = 27^\circ\text{C}$ তাপমাত্রার বায়ুমণ্ডলে তাপ বর্জন করে। রেফ্রিজারেটরটির কার্যসম্পাদন সহগ বা গুণক ($COP = \frac{T_2}{T_1 - T_2}$) কত?</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+একটি সিলিন্ডারে ঘর্ষণহীন পিস্টনের অধীনে $1.0\text{ atm}$ ধ্রুব চাপে $0.5\text{ মোল}$ গ্যাসকে উত্তপ্ত করে তাপমাত্রা $20^\circ\text{C}$ হতে $120^\circ\text{C}$ করা হলো। গ্যাসের প্রসারণে কৃতকাজ $W$ নির্ণয় কর। ($R = 8.314\text{ J/mol}\cdot\text{K}$)।</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 4)।</t>
+          <t>সমচাপ প্রক্রিয়ায় কৃতকাজ $W = P\Delta V = n R \Delta T$। তাপমাত্রা বৃদ্ধি $\Delta T = 120 - 20 = 100\text{ K}$। $W = 0.5 \times 8.314 \times 100 = 415.7\text{ J}$।</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 4</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>কৃতকাজ $W = 415.7\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3871,7 +3624,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>সমোষ্ণ প্রক্রিয়ায় কৃতকাজ ও তাপ (সমস্যা 5)</t>
+          <t>তাপগতিবিদ্যার ১ম সূত্র ও তাপগতীয় প্রক্রিয়াসমূহ (1st Law &amp; Processes)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3880,29 +3633,29 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[সমস্যা 5: সমোষ্ণ প্রক্রিয়ায় কৃতকাজ ও তাপ]
-$V_1 = 1.0\text{ L}$ আয়তনের একটি আদর্শ গ্যাসকে স্থির তাপমাত্রা $T = 1200\text{ K}$-এ সমোষ্ণ প্রক্রিয়ায় প্রসারিত করে আয়তন $V_2 = 1.0\text{ L}$ করা হলো। গ্যাসে প্রদত্ত তাপশক্তি ও কৃতকাজ $W = nRT \ln(V_2/V_1)$ কত? ($n = 1\text{ mol}$)</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##
+একটি একপরমাণুক আদর্শ গ্যাসের ($\gamma = 5/3 = 1.67$) $1.0\text{ মোল}$ গ্যাসকে রুদ্ধতাপীয় প্রক্রিয়ায় প্রসারিত করা হলো যাতে তার তাপমাত্রা $400\text{ K}$ হতে নেমে $300\text{ K}$ হয়। এই রুদ্ধতাপীয় প্রসারণে গ্যাস কর্তৃক সম্পাদিত কাজ কত?</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 5)।</t>
+          <t>রুদ্ধতাপীয় প্রক্রিয়ায় কৃতকাজ $W = \frac{nR(T_1 - T_2)}{\gamma - 1} = \frac{1.0 \times 8.314 \times (400 - 300)}{5/3 - 1} = \frac{831.4}{2/3} = 831.4 \times 1.5 = 1247.1\text{ J}$।</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 5</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>কৃতকাজ $W = 1247.1\text{ J} \approx 1.25\text{ kJ}$</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3922,12 +3675,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>পানি বাষ্পীভবনে এন্ট্রপি বৃদ্ধি (সমস্যা 6)</t>
+          <t>তাপগতিবিদ্যার ১ম সূত্র ও তাপগতীয় প্রক্রিয়াসমূহ (1st Law &amp; Processes)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -3935,25 +3688,25 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[সমস্যা 6: পানি বাষ্পীভবনে এন্ট্রপি বৃদ্ধি]
-$100^\circ\text{C}$ তাপমাত্রার $200\text{ g}$ পানিকে ফুটন্ত অবস্থায় সম-তাপমাত্রার বাষ্পে পরিণত করা হলো। এই প্রক্রিয়ায় এন্ট্রপির পরিবর্তন কত? (বাষ্পীভবনের সুপ্ততাপ $L_v = 2.26 \times 10^6\text{ J/kg}$)</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>##GEO:triangle[b=4,h=3][size:small]##
+একটি $P-V$ চিত্রে একটি গ্যাস চক্রাকারে $A 	o B 	o C 	o A$ পথে আবর্তিত হয়। $A(P_1 = 1.0	imes 10^5	ext{ Pa}, V_1 = 2.0	ext{ m}^3)$, $B(P_2 = 4.0	imes 10^5	ext{ Pa}, V_2 = 2.0	ext{ m}^3)$, এবং $C(P_3 = 1.0	imes 10^5	ext{ Pa}, V_3 = 6.0	ext{ m}^3)$। প্রতি চক্রে গ্যাস কর্তৃক মোট কৃতকাজ কত?</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>##GEO:triangle[b=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 6)।</t>
+          <t>ত্রিভুজাকার চক্রের ক্ষেত্রফলই প্রতি চক্রে কৃত মোট কাজ: $W = \frac{1}{2} \times \text{ভূমি} \times \text{উচ্চতা} = \frac{1}{2}(V_3 - V_1)(P_2 - P_1) = \frac{1}{2}(6.0 - 2.0)(4.0 \times 10^5 - 1.0 \times 10^5) = \frac{1}{2}(4.0)(3.0 \times 10^5) = 6.0 \times 10^5\text{ J} = 600.0\text{ kJ}$।</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 6</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>প্রতি চক্রে মোট কৃতকাজ $W = 6.0 \times 10^5\text{ J} = 600.0\text{ kJ}$</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3973,7 +3726,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম সূত্র ও অভ্যন্তরীণ শক্তি (সমস্যা 7)</t>
+          <t>তাপগতিবিদ্যার ১ম সূত্র ও তাপগতীয় প্রক্রিয়াসমূহ (1st Law &amp; Processes)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3982,29 +3735,29 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[সমস্যা 7: তাপগতিবিদ্যার ১ম সূত্র ও অভ্যন্তরীণ শক্তি]
-একটি আবদ্ধ গ্যাস ব্যবস্থায় বাইরে হতে $\Delta Q = 450\text{ J}$ তাপশক্তি সরবরাহ করা হলো এবং ব্যবস্থাটি সম্প্রসারিত হয়ে $\Delta W = 500\text{ J}$ কাজ সম্পাদন করল। ব্যবস্থার অভ্যন্তরীণ শক্তির পরিবর্তন $\Delta U = \Delta Q - \Delta W$ কত?</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+সমোষ্ণ রেখা এবং রুদ্ধতাপীয় রেখার ঢালের অনুপাত প্রমাণ কর: দেখাও যে রুদ্ধতাপীয় রেখা সমোষ্ণ রেখার চেয়ে $\gamma$ গুণ খাড়া ($\left(\frac{dP}{dV}\right)_{\text{adi}} = \gamma \left(\frac{dP}{dV}\right)_{\text{iso}}$)। $\gamma = 1.4$ বিশিষ্ট গ্যাসের জন্য রুদ্ধতাপীয় ঢাল সমোষ্ণ ঢালের কত গুণ?</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 7)।</t>
+          <t>সমোষ্ণ প্রক্রিয়ায় $PV = \text{ধ্রুবক} \implies P dV + V dP = 0 \implies \left(\frac{dP}{dV}\right)_{\text{iso}} = -\frac{P}{V}$। রুদ্ধতাপীয় প্রক্রিয়ায় $P V^\gamma = \text{ধ্রুবক} \implies V^\gamma dP + \gamma P V^{\gamma-1} dV = 0 \implies \left(\frac{dP}{dV}\right)_{\text{adi}} = -\gamma \frac{P}{V} = \gamma \left(\frac{dP}{dV}\right)_{\text{iso}}$। অতএব $\gamma = 1.4$ হলে ঢাল ঠিক $1.4$ গুণ খাড়া।</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 7</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>রুদ্ধতাপীয় ঢাল সমোষ্ণ ঢালের $1.40$ গুণ খাড়া</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4024,12 +3777,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>দ্বি-পরমাণুক গ্যাসের গামা ও রূদ্ধতাপীয় সমীকরণ (সমস্যা 8)</t>
+          <t>তাপগতিবিদ্যার ১ম সূত্র ও তাপগতীয় প্রক্রিয়াসমূহ (1st Law &amp; Processes)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -4037,25 +3790,25 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>[সমস্যা 8: দ্বি-পরমাণুক গ্যাসের গামা ও রূদ্ধতাপীয় সমীকরণ]
-একটি দ্বি-পরমাণুক গ্যাসের জন্য $\gamma = 1.4$। গ্যাসটির প্রারম্ভিক চাপ $P_1 = 1\text{ atm}$ এবং আয়তন $V_1$ হতে রূদ্ধতাপীয় প্রক্রিয়ায় আয়তন সংকুচিত করে এক-চতুর্থাংশ ($V_2 = V_1 / 4$) করা হলে চূড়ান্ত চাপ $P_2 = P_1 (V_1/V_2)^\gamma$ কত অ্যাটমস্ফিয়ার হবে?</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি গ্যাসকে রুদ্ধতাপীয়ভাবে সংকুচিত করায় তার তাপমাত্রা এমনভাবে বৃদ্ধি পেল যে অন্তিম পরম তাপমাত্রা আদি পরম তাপমাত্রার দ্বিগুণ হলো। যদি $\gamma = 1.5$ হয়, তবে গ্যাসের আদি ও অন্তিম আয়তনের অনুপাত $V_1 : V_2$ কত?</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 8)।</t>
+          <t>$T_1 V_1^{\gamma-1} = T_2 V_2^{\gamma-1} \implies \left(\frac{V_1}{V_2}\right)^{\gamma-1} = \frac{T_2}{T_1} = 2$। $\gamma = 1.5$ হওয়ায় $\gamma - 1 = 0.5 = 1/2$। $\left(\frac{V_1}{V_2}\right)^{1/2} = 2 \implies \frac{V_1}{V_2} = 2^2 = 4$। অর্থাৎ $V_1 : V_2 = 4 : 1$।</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 8</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>$V_1 : V_2 = 4 : 1$</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4075,7 +3828,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>কার্নো ইঞ্জিনের গ্রাহকের তাপমাত্রা পরিবর্তন (সমস্যা 9)</t>
+          <t>তাপগতিবিদ্যার ১ম সূত্র ও তাপগতীয় প্রক্রিয়াসমূহ (1st Law &amp; Processes)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4084,29 +3837,29 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[সমস্যা 9: কার্নো ইঞ্জিনের গ্রাহকের তাপমাত্রা পরিবর্তন]
-একটি কার্নো ইঞ্জিনের বর্তমান দক্ষতা $80\%$। তাপগ্রাহকের তাপমাত্রা $90\text{ K}$ হ্রাস করলে ইঞ্জিনের নতুন দক্ষতা কত বৃদ্ধি পাবে, যদি উৎসের তাপমাত্রা $T_1 = 600\text{ K}$ স্থির থাকে?</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##
+স্থির চাপে $2.0\text{ মোল}$ হিলিয়াম গ্যাসকে ($C_v = 1.5 R, C_p = 2.5 R$) উত্তপ্ত করে তাপমাত্রা $50\text{ K}$ বৃদ্ধি করা হলো। সরবরাহকৃত তাপ $Q$, সম্পাদিত কাজ $W$ এবং অভ্যন্তরীণ শক্তি বৃদ্ধি $\Delta U$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 9)।</t>
+          <t>সরবরাহকৃত তাপ $Q = n C_p \Delta T = 2.0 \times (2.5 \times 8.314) \times 50 = 2078.5\text{ J}$। সম্পাদিত কাজ $W = P\Delta V = n R \Delta T = 2.0 \times 8.314 \times 50 = 831.4\text{ J}$। অভ্যন্তরীণ শক্তির বৃদ্ধি $\Delta U = n C_v \Delta T = 2.0 \times (1.5 \times 8.314) \times 50 = 1247.1\text{ J}$। ১ম সূত্র যাচাই: $Q = \Delta U + W = 1247.1 + 831.4 = 2078.5\text{ J}$।</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 9</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>$Q = 2078.5\text{ J}, W = 831.4\text{ J}, \Delta U = 1247.1\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4126,12 +3879,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>থার্মোমিটারের মৌলিক ব্যবধান ও পরম শূন্য (সমস্যা 10)</t>
+          <t>তাপগতিবিদ্যার ১ম সূত্র ও তাপগতীয় প্রক্রিয়াসমূহ (1st Law &amp; Processes)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -4139,25 +3892,25 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[সমস্যা 10: থার্মোমিটারের মৌলিক ব্যবধান ও পরম শূন্য]
-একটি ত্রুটিপূর্ণ থার্মোমিটার গলিত বরফে $10^\circ\text{C}$ এবং প্রমাণ চাপে বাষ্পে $91^\circ\text{C}$ পাঠ প্রদর্শন করে। থার্মোমিটারটি $50^\circ\text{C}$ পাঠ দিলে ফারেনহাইট স্কেলে এর সঠিক মান কত?</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি দ্বিপরমাণুক গ্যাসের $C_p$ এবং $C_v$-এর মান নির্ণয় কর। ১ মোল গ্যাসকে স্থির আয়তনে $100^\circ\text{C}$ উত্তপ্ত করলে কত জুল তাপ প্রয়োজন? ($R = 8.314\text{ J/mol}\cdot\text{K}$)।</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 10)।</t>
+          <t>দ্বিপরমাণুক গ্যাসে $f = 5$ হওয়ায় $C_v = \frac{5}{2}R = 2.5(8.314) = 20.785\text{ J/mol}\cdot\text{K}$। $C_p = C_v + R = 3.5(8.314) = 29.099\text{ J/mol}\cdot\text{K}$। স্থির আয়তনে $W = 0$, ফলে $Q = \Delta U = n C_v \Delta T = 1.0 \times 20.785 \times 100 = 2078.5\text{ J}$।</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 10</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>$C_v = 20.785\text{ J/mol}\cdot\text{K}, C_p = 29.099\text{ J/mol}\cdot\text{K}$, প্রয়োজনীয় তাপ $Q = 2078.5\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4177,44 +3930,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>কার্নো চক্র ও সর্বোচ্চ কর্মদক্ষতা (সমস্যা 11)</t>
+          <t>কার্নো চক্র, দক্ষতা ও রেফ্রিজারেটর (Carnot Engine, Efficiency &amp; COP)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>##PRESET:carnot-cycle[size:medium]##
-[সমস্যা 11: কার্নো চক্র ও সর্বোচ্চ কর্মদক্ষতা]
-##PRESET:carnot-cycle[size:medium]##
-একটি কার্নো ইঞ্জিন $T_1 = 1200\text{ K}$ তাপমাত্রার তাপ উৎস হতে $Q_1 = 3000\text{ J}$ তাপ গ্রহণ করে এবং $T_2 = 300\text{ K}$ তাপমাত্রার গ্রাহকে তাপ বর্জন করে। ইঞ্জিনটির কর্মদক্ষতা ($\ eta = 1 - T_2/T_1$) এবং প্রতি চক্রে সম্পাদিত কাজের মান কত?</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি কার্নো ইঞ্জিন $500\text{ K}$ এবং $300\text{ K}$ তাপমাত্রার দুটি আধারের মধ্যে কাজ করে। ইঞ্জিনটির দক্ষতা $\eta$ কত? ইঞ্জিনটি যদি উৎস থেকে প্রতি চক্রে $1200\text{ J}$ তাপ গ্রহণ করে, তবে প্রতি চক্রে সম্পাদিত কাজ $W$ এবং গ্রাহকে বর্জিত তাপ $Q_2$ কত?</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>##PRESET:carnot-cycle[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 11)।</t>
+          <t>কার্নো ইঞ্জিনের দক্ষতা $\eta = 1 - \frac{T_2}{T_1} = 1 - \frac{300}{500} = 1 - 0.6 = 0.40 = 40.0\%$। সম্পাদিত কাজ $W = \eta Q_1 = 0.40 \times 1200 = 480.0\text{ J}$। গ্রাহকে বর্জিত তাপ $Q_2 = Q_1 - W = 1200 - 480 = 720.0\text{ J}$।</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 11</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>দক্ষতা $\eta = 40.0\%$, কাজ $W = 480.0\text{ J}$, বর্জিত তাপ $Q_2 = 720.0\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4234,7 +3981,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>বরফ গলন ও তাপমাত্রা বৃদ্ধিতে এন্ট্রপি (সমস্যা 12)</t>
+          <t>কার্নো চক্র, দক্ষতা ও রেফ্রিজারেটর (Carnot Engine, Efficiency &amp; COP)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4247,25 +3994,25 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>[সমস্যা 12: বরফ গলন ও তাপমাত্রা বৃদ্ধিতে এন্ট্রপি]
-$0^\circ\text{C}$ তাপমাত্রার $20\text{ g}$ বরফকে $50^\circ\text{C}$ তাপমাত্রার পানিতে রূপান্তরিত করা হলো। এই সামগ্রিক প্রক্রিয়ায় মোট এন্ট্রপির পরিবর্তন ($\Delta S$) কত জুল/কেলভিন? ($L_f = 3.36 \times 10^5\text{ J/kg}, s = 4200\text{ J/(kg}\cdot\text{K)}$)</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি কার্নো ইঞ্জিনের দক্ষতা $40\%$। গ্রাহকের তাপমাত্রা অপরিবর্তিত রেখে উৎসের তাপমাত্রা কত বৃদ্ধি করতে হবে যাতে দক্ষতা বেড়ে $50\%$ হয়? গ্রাহকের আদি তাপমাত্রা $27^\circ\text{C}$ হলে উৎসের আদি ও পরিবর্তিত তাপমাত্রা নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 12)।</t>
+          <t>গ্রাহকের তাপমাত্রা $T_2 = 273 + 27 = 300\text{ K}$। $\eta_1 = 1 - \frac{T_2}{T_1} = 0.40 \implies \frac{300}{T_1} = 0.60 \implies T_1 = \frac{300}{0.60} = 500\text{ K}$। নতুন দক্ষতা $\eta_2 = 0.50 \implies 1 - \frac{300}{T_1'} = 0.50 \implies \frac{300}{T_1'} = 0.50 \implies T_1' = \frac{300}{0.50} = 600\text{ K}$। তাপমাত্রা বৃদ্ধি $\Delta T_1 = 600 - 500 = 100.0\text{ K}$।</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 12</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>আদি উৎসের তাপমাত্রা $T_1 = 500.0\text{ K} = 227^\circ\text{C}$, নতুন উৎসের তাপমাত্রা $T_1' = 600.0\text{ K} = 327^\circ\text{C}$ (বৃদ্ধি $= 100.0\text{ K}$)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4285,44 +4032,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>রূদ্ধতাপীয় প্রসারণ ও কাজের হিসাব (সমস্যা 13)</t>
+          <t>কার্নো চক্র, দক্ষতা ও রেফ্রিজারেটর (Carnot Engine, Efficiency &amp; COP)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>##PRESET:heat-engine[size:medium]##
-[সমস্যা 13: রূদ্ধতাপীয় প্রসারণ ও কাজের হিসাব]
-##PRESET:heat-engine[size:medium]##
-$1\text{ mol}$ হিলিয়াম গ্যাস ($C_v = 1.5R$) প্রারম্ভিক তাপমাত্রা $T_1 = 400\text{ K}$ হতে রূদ্ধতাপীয় প্রক্রিয়ায় প্রসারিত হয়ে তাপমাত্রা $T_2 = 700\text{ K}$-এ নেমে এলো। গ্যাস কর্তৃক সম্পাদিত কাজের মান $W = n C_v(T_1 - T_2)$ কত জুল? ($R = 8.314\text{ J/(mol}\cdot\text{K)}$)</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+কোনো কার্নো ইঞ্জিনের উৎসের তাপমাত্রা অপরিবর্তিত রেখে গ্রাহকের তাপমাত্রা $50\text{ K}$ হ্রাস করলে এর দক্ষতা $30\%$ হতে বৃদ্ধি পেয়ে $40\%$ হয়। তাপ উৎস ও তাপ গ্রাহকের প্রারম্ভিক তাপমাত্রা কত ছিল?</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>##PRESET:heat-engine[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 13)।</t>
+          <t>১ম ক্ষেত্রে: $1 - \frac{T_2}{T_1} = 0.30 \implies \frac{T_2}{T_1} = 0.70$। ২য় ক্ষেত্রে: $1 - \frac{T_2 - 50}{T_1} = 0.40 \implies \frac{T_2 - 50}{T_1} = 0.60$। বিয়োগ করে: $\frac{50}{T_1} = 0.70 - 0.60 = 0.10 \implies T_1 = \frac{50}{0.10} = 500.0\text{ K}$। গ্রাহকের আদি তাপমাত্রা $T_2 = 0.70 T_1 = 0.70 \times 500 = 350.0\text{ K}$।</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 13</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>উৎসের তাপমাত্রা $T_1 = 500.0\text{ K}$, গ্রাহকের আদি তাপমাত্রা $T_2 = 350.0\text{ K}$</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4342,7 +4083,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>রেফ্রিজারেটরের কার্যসম্পাদন গুণক (COP) (সমস্যা 14)</t>
+          <t>কার্নো চক্র, দক্ষতা ও রেফ্রিজারেটর (Carnot Engine, Efficiency &amp; COP)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4355,25 +4096,25 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[সমস্যা 14: রেফ্রিজারেটরের কার্যসম্পাদন গুণক (COP)]
-একটি আদর্শ রেফ্রিজারেটর $T_2 = -6^\circ\text{C}$ তাপমাত্রা হতে তাপ শোষণ করে $T_1 = 27^\circ\text{C}$ তাপমাত্রার বায়ুমণ্ডলে তাপ বর্জন করে। রেফ্রিজারেটরটির কার্যসম্পাদন সহগ বা গুণক ($COP = \frac{T_2}{T_1 - T_2}$) কত?</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি তাপ ইঞ্জিনের কর্মদক্ষতা $\eta = 35\%$। এটি প্রতি মিনিটে $1.8 \times 10^7\text{ J}$ তাপ শক্তি সরবরাহ পেলে ইঞ্জিনটির আউটপুট মেকানিক্যাল পাওয়ার (Output power in kW) কত?</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 14)।</t>
+          <t>প্রতি সেকেন্ডে গৃহীত তাপ $Q_1 = \frac{1.8 \times 10^7\text{ J}}{60\text{ s}} = 3.0 \times 10^5\text{ W} = 300\text{ kW}$। আউটপুট মেকানিক্যাল পাওয়ার $P = \eta Q_1 = 0.35 \times 300\text{ kW} = 105.0\text{ kW}$।</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 14</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>আউটপুট ক্ষমতা $P = 105.0\text{ kW}$</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4393,38 +4134,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>সমোষ্ণ প্রক্রিয়ায় কৃতকাজ ও তাপ (সমস্যা 15)</t>
+          <t>কার্নো চক্র, দক্ষতা ও রেফ্রিজারেটর (Carnot Engine, Efficiency &amp; COP)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[সমস্যা 15: সমোষ্ণ প্রক্রিয়ায় কৃতকাজ ও তাপ]
-$V_1 = 1.0\text{ L}$ আয়তনের একটি আদর্শ গ্যাসকে স্থির তাপমাত্রা $T = 800\text{ K}$-এ সমোষ্ণ প্রক্রিয়ায় প্রসারিত করে আয়তন $V_2 = 1.0\text{ L}$ করা হলো। গ্যাসে প্রদত্ত তাপশক্তি ও কৃতকাজ $W = nRT \ln(V_2/V_1)$ কত? ($n = 1\text{ mol}$)</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=3][size:small]##
+দুটি কার্নো ইঞ্জিন $A$ ও $B$ শ্রেণিতে যুক্ত। ইঞ্জিন $A$ $T_1 = 800\text{ K}$ হতে তাপ গ্রহণ করে এবং $T$ তাপমাত্রায় বর্জিত তাপ ইঞ্জিন $B$-তে সরবরাহ করে, যা $T_2 = 200\text{ K}$ তাপমাত্রায় বর্জন করে। যদি উভয় ইঞ্জিনের সম্পাদিত কাজ সমান হয় ($W_A = W_B$), তবে মধ্যবর্তী তাপমাত্রা $T$ কত?</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 15)।</t>
+          <t>ইঞ্জিনদ্বয় সমান কাজ করলে: $W_A = Q_1 - Q = W_B = Q - Q_2$। কার্নো ইঞ্জিনের তাপ ও তাপমাত্রার অনুপাত হতে: $\frac{Q_1}{T_1} = \frac{Q}{T} = \frac{Q_2}{T_2} = k$। অতএব $k(T_1 - T) = k(T - T_2) \implies T_1 - T = T - T_2 \implies 2T = T_1 + T_2 \implies T = \frac{T_1 + T_2}{2} = \frac{800 + 200}{2} = 500.0\text{ K}$।</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 15</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>মধ্যবর্তী তাপমাত্রা $T = 500.0\text{ K}$</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4444,7 +4185,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>পানি বাষ্পীভবনে এন্ট্রপি বৃদ্ধি (সমস্যা 16)</t>
+          <t>কার্নো চক্র, দক্ষতা ও রেফ্রিজারেটর (Carnot Engine, Efficiency &amp; COP)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4457,25 +4198,25 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[সমস্যা 16: পানি বাষ্পীভবনে এন্ট্রপি বৃদ্ধি]
-$100^\circ\text{C}$ তাপমাত্রার $1000\text{ g}$ পানিকে ফুটন্ত অবস্থায় সম-তাপমাত্রার বাষ্পে পরিণত করা হলো। এই প্রক্রিয়ায় এন্ট্রপির পরিবর্তন কত? (বাষ্পীভবনের সুপ্ততাপ $L_v = 2.26 \times 10^6\text{ J/kg}$)</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=3][size:small]##
+উপরের সমস্যায় যদি উভয় ইঞ্জিনের দক্ষতা সমান হয় ($\eta_A = \eta_B$), তবে মধ্যবর্তী তাপমাত্রা $T$ কত হবে?</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 16)।</t>
+          <t>দক্ষতা সমান হলে: $1 - \frac{T}{T_1} = 1 - \frac{T_2}{T} \implies \frac{T}{T_1} = \frac{T_2}{T} \implies T^2 = T_1 T_2 \implies T = \sqrt{T_1 T_2}$। মান বসিয়ে: $T = \sqrt{800 \times 200} = \sqrt{160000} = 400.0\text{ K}$।</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 16</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>মধ্যবর্তী তাপমাত্রা $T = 400.0\text{ K}$</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4495,38 +4236,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম সূত্র ও অভ্যন্তরীণ শক্তি (সমস্যা 17)</t>
+          <t>কার্নো চক্র, দক্ষতা ও রেফ্রিজারেটর (Carnot Engine, Efficiency &amp; COP)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[সমস্যা 17: তাপগতিবিদ্যার ১ম সূত্র ও অভ্যন্তরীণ শক্তি]
-একটি আবদ্ধ গ্যাস ব্যবস্থায় বাইরে হতে $\Delta Q = 1250\text{ J}$ তাপশক্তি সরবরাহ করা হলো এবং ব্যবস্থাটি সম্প্রসারিত হয়ে $\Delta W = 500\text{ J}$ কাজ সম্পাদন করল। ব্যবস্থার অভ্যন্তরীণ শক্তির পরিবর্তন $\Delta U = \Delta Q - \Delta W$ কত?</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি কার্নো ইঞ্জিন পানি জমাট বাঁধার তাপমাত্রা ($0^\circ\text{C}$) এবং স্ফুটনাঙ্কের ($100^\circ\text{C}$) মধ্যে কাজ করে। ইঞ্জিনটির তাত্ত্বিক সর্বোচ্চ দক্ষতা কত? যদি ইঞ্জিনটিকে বিপরীতক্রমে রেফ্রিজারেটর হিসেবে চালানো হয়, তবে এর কার্যসম্পাদন গুণক (Coefficient of Performance $\beta$) কত?</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 17)।</t>
+          <t>$T_1 = 273.15 + 100 = 373.15\text{ K}$, $T_2 = 273.15\text{ K}$। দক্ষতা $\eta = 1 - \frac{273.15}{373.15} = \frac{100}{373.15} \approx 0.2680 \approx 26.81\%$। রেফ্রিজারেটরের COP $\beta = \frac{T_2}{T_1 - T_2} = \frac{273.15}{100} = 2.7315 \approx 2.73$।</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 17</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>দক্ষতা $\eta = 26.81\%$, রেফ্রিজারেটরের $\beta = 2.73$</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4546,7 +4287,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>দ্বি-পরমাণুক গ্যাসের গামা ও রূদ্ধতাপীয় সমীকরণ (সমস্যা 18)</t>
+          <t>কার্নো চক্র, দক্ষতা ও রেফ্রিজারেটর (Carnot Engine, Efficiency &amp; COP)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4559,25 +4300,25 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[সমস্যা 18: দ্বি-পরমাণুক গ্যাসের গামা ও রূদ্ধতাপীয় সমীকরণ]
-একটি দ্বি-পরমাণুক গ্যাসের জন্য $\gamma = 1.4$। গ্যাসটির প্রারম্ভিক চাপ $P_1 = 1\text{ atm}$ এবং আয়তন $V_1$ হতে রূদ্ধতাপীয় প্রক্রিয়ায় আয়তন সংকুচিত করে এক-চতুর্থাংশ ($V_2 = V_1 / 4$) করা হলে চূড়ান্ত চাপ $P_2 = P_1 (V_1/V_2)^\gamma$ কত অ্যাটমস্ফিয়ার হবে?</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি রেফ্রিজারেটর $4^\circ\text{C}$ অভ্যন্তরীণ তাপমাত্রা থেকে তাপ অপসারণ করে $30^\circ\text{C}$ তাপমাত্রার ঘরে তাপ বর্জন করে। রেফ্রিজারেটরটির কার্যসম্পাদন গুণক (COP) কত? প্রতি সেকেন্ডে অভ্যন্তরীণ প্রকোষ্ঠ হতে $1000\text{ J}$ তাপ অপসারণ করতে মোট কত ওয়াট বৈদ্যুতিক ক্ষমতার মোটর প্রয়োজন?</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 18)।</t>
+          <t>$T_2 = 273 + 4 = 277\text{ K}$, $T_1 = 273 + 30 = 303\text{ K}$। $\beta = \frac{T_2}{T_1 - T_2} = \frac{277}{303 - 277} = \frac{277}{26} \approx 10.654$। কাজ $W = \frac{Q_2}{\beta} = \frac{1000\text{ J}}{10.654} \approx 93.86\text{ J/s} = 93.86\text{ W}$।</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 18</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>$\text{COP} \beta = 10.66$, প্রয়োজনীয় ক্ষমতা $P = 93.81\text{ W}$</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4597,38 +4338,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>কার্নো ইঞ্জিনের গ্রাহকের তাপমাত্রা পরিবর্তন (সমস্যা 19)</t>
+          <t>কার্নো চক্র, দক্ষতা ও রেফ্রিজারেটর (Carnot Engine, Efficiency &amp; COP)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[সমস্যা 19: কার্নো ইঞ্জিনের গ্রাহকের তাপমাত্রা পরিবর্তন]
-একটি কার্নো ইঞ্জিনের বর্তমান দক্ষতা $40\%$। তাপগ্রাহকের তাপমাত্রা $90\text{ K}$ হ্রাস করলে ইঞ্জিনের নতুন দক্ষতা কত বৃদ্ধি পাবে, যদি উৎসের তাপমাত্রা $T_1 = 600\text{ K}$ স্থির থাকে?</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+কার্নো উপপাদ্য অনুসারে দেখাও যে একই তাপমাত্রার দুটি আধারের মধ্যে কর্মরত কোনো ইঞ্জিনই একটি প্রত্যাবর্তী কার্নো ইঞ্জিনের চেয়ে বেশি দক্ষ হতে পারে না। যদি কোনো উদ্ভাবক $600\text{ K}$ এবং $300\text{ K}$-এর মধ্যে একটি ইঞ্জিনের দক্ষতা $60\%$ দাবি করেন, তবে তাপগতিবিদ্যার কোন সূত্র লঙ্ঘিত হয়?</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 19)।</t>
+          <t>কার্নো ইঞ্জিনের দক্ষতা $\eta_{\max} = 1 - \frac{T_2}{T_1} = 1 - \frac{300}{600} = 0.50 = 50.0\%$। যেকোনো অপ্রত্যাবর্তী ইঞ্জিনের দক্ষতা $\eta \le 50\%$। উদ্ভাবকের দাবি $60\% &gt; 50\%$, যা ক্লসিয়াসের উপপাদ্য এবং তাপগতিবিদ্যার ২য় সূত্রকে সরাসরি লঙ্ঘন করায় এটি অসম্ভব।</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 19</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>সর্বোচ্চ সম্ভাব্য দক্ষতা $50.0\%$, উদ্ভাবকের দাবি তাপগতিবিদ্যার ২য় সূত্র (ক্লসিয়াস ও কেলভিন-প্ল্যাঙ্ক বিবৃতি) লঙ্ঘন করে</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4648,7 +4389,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>থার্মোমিটারের মৌলিক ব্যবধান ও পরম শূন্য (সমস্যা 20)</t>
+          <t>কার্নো চক্র, দক্ষতা ও রেফ্রিজারেটর (Carnot Engine, Efficiency &amp; COP)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4661,25 +4402,25 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[সমস্যা 20: থার্মোমিটারের মৌলিক ব্যবধান ও পরম শূন্য]
-একটি ত্রুটিপূর্ণ থার্মোমিটার গলিত বরফে $6^\circ\text{C}$ এবং প্রমাণ চাপে বাষ্পে $91^\circ\text{C}$ পাঠ প্রদর্শন করে। থার্মোমিটারটি $50^\circ\text{C}$ পাঠ দিলে ফারেনহাইট স্কেলে এর সঠিক মান কত?</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি আদর্শ কার্নো ইঞ্জিন প্রতি চক্রে পরিবেশ থেকে $500\text{ cal}$ তাপ গ্রহণ করে এবং $400\text{ cal}$ তাপ বর্জন করে। যদি গ্রাহকের তাপমাত্রা $-3^\circ\text{C}$ হয়, তবে উৎসের তাপমাত্রা কত ডিগ্রি সেলসিয়াস ছিল?</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 20)।</t>
+          <t>গ্রাহকের তাপমাত্রা $T_2 = 273 - 3 = 270\text{ K}$। কার্নো চক্রে $\frac{Q_1}{Q_2} = \frac{T_1}{T_2} \implies \frac{500}{400} = \frac{T_1}{270} \implies T_1 = 270 \times 1.25 = 337.5\text{ K}$। সেলসিয়াসে $\theta_1 = 337.5 - 273 = 64.5^\circ\text{C}$।</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 20</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>উৎসের তাপমাত্রা $T_1 = 337.5\text{ K} = 64.5^\circ\text{C}$</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4699,44 +4440,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>কার্নো চক্র ও সর্বোচ্চ কর্মদক্ষতা (সমস্যা 21)</t>
+          <t>এন্ট্রপি পরিবর্তন, সুপ্ততাপ ও ২য় সূত্র (Entropy Changes &amp; 2nd Law)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>##PRESET:carnot-cycle[size:medium]##
-[সমস্যা 21: কার্নো চক্র ও সর্বোচ্চ কর্মদক্ষতা]
-##PRESET:carnot-cycle[size:medium]##
-একটি কার্নো ইঞ্জিন $T_1 = 800\text{ K}$ তাপমাত্রার তাপ উৎস হতে $Q_1 = 3000\text{ J}$ তাপ গ্রহণ করে এবং $T_2 = 300\text{ K}$ তাপমাত্রার গ্রাহকে তাপ বর্জন করে। ইঞ্জিনটির কর্মদক্ষতা ($\ eta = 1 - T_2/T_1$) এবং প্রতি চক্রে সম্পাদিত কাজের মান কত?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+$0^\circ\text{C}$ তাপমাত্রার $100\text{ g}$ বরফকে গলিয়ে $0^\circ\text{C}$ তাপমাত্রার পানিতে পরিণত করা হলো। এই প্রক্রিয়ায় এন্ট্রপির পরিবর্তন $\Delta S$ নির্ণয় কর। (বরফ গলনের সুপ্ততাপ $L_f = 3.36 \times 10^5\text{ J/kg}$)।</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>##PRESET:carnot-cycle[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 21)।</t>
+          <t>ভর $m = 0.10\text{ kg}$, তাপমাত্রা স্থির $T = 273.15\text{ K}$। শোষিত তাপ $Q = m L_f = 0.10 \times 3.36 \times 10^5 = 33600\text{ J}$। এন্ট্রপির পরিবর্তন $\Delta S = \frac{Q}{T} = \frac{33600}{273.15} \approx 123.01\text{ J/K}$।</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 21</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>এন্ট্রপির পরিবর্তন $\Delta S = 123.01\text{ J/K}$</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4756,12 +4491,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>বরফ গলন ও তাপমাত্রা বৃদ্ধিতে এন্ট্রপি (সমস্যা 22)</t>
+          <t>এন্ট্রপি পরিবর্তন, সুপ্ততাপ ও ২য় সূত্র (Entropy Changes &amp; 2nd Law)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -4769,25 +4504,25 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[সমস্যা 22: বরফ গলন ও তাপমাত্রা বৃদ্ধিতে এন্ট্রপি]
-$0^\circ\text{C}$ তাপমাত্রার $100\text{ g}$ বরফকে $50^\circ\text{C}$ তাপমাত্রার পানিতে রূপান্তরিত করা হলো। এই সামগ্রিক প্রক্রিয়ায় মোট এন্ট্রপির পরিবর্তন ($\Delta S$) কত জুল/কেলভিন? ($L_f = 3.36 \times 10^5\text{ J/kg}, s = 4200\text{ J/(kg}\cdot\text{K)}$)</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+$100^\circ\text{C}$ তাপমাত্রার $50\text{ g}$ পানিকে বাষ্পীভূত করে $100^\circ\text{C}$ তাপমাত্রার বাষ্পে পরিণত করা হলে এন্ট্রপির বৃদ্ধি কত? (বাষ্পীভবনের সুপ্ততাপ $L_v = 2.26 \times 10^6\text{ J/kg}$)।</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 22)।</t>
+          <t>ভর $m = 0.05\text{ kg}$, স্থির তাপমাত্রা $T = 373.15\text{ K}$। প্রয়োজনীয় তাপ $Q = m L_v = 0.05 \times 2.26 \times 10^6 = 113000\text{ J}$। এন্ট্রপির বৃদ্ধি $\Delta S = \frac{Q}{T} = \frac{113000}{373.15} \approx 302.83\text{ J/K}$।</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 22</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>এন্ট্রপির বৃদ্ধি $\Delta S = 302.83\text{ J/K}$</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4807,44 +4542,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>রূদ্ধতাপীয় প্রসারণ ও কাজের হিসাব (সমস্যা 23)</t>
+          <t>এন্ট্রপি পরিবর্তন, সুপ্ততাপ ও ২য় সূত্র (Entropy Changes &amp; 2nd Law)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>##PRESET:heat-engine[size:medium]##
-[সমস্যা 23: রূদ্ধতাপীয় প্রসারণ ও কাজের হিসাব]
-##PRESET:heat-engine[size:medium]##
-$1\text{ mol}$ হিলিয়াম গ্যাস ($C_v = 1.5R$) প্রারম্ভিক তাপমাত্রা $T_1 = 1200\text{ K}$ হতে রূদ্ধতাপীয় প্রক্রিয়ায় প্রসারিত হয়ে তাপমাত্রা $T_2 = 700\text{ K}$-এ নেমে এলো। গ্যাস কর্তৃক সম্পাদিত কাজের মান $W = n C_v(T_1 - T_2)$ কত জুল? ($R = 8.314\text{ J/(mol}\cdot\text{K)}$)</t>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##
+$0^\circ\text{C}$ তাপমাত্রার $1.0\text{ kg}$ পানিকে উত্তপ্ত করে $100^\circ\text{C}$-এ উন্নীত করা হলো। পানির এন্ট্রপির মোট পরিবর্তন $\Delta S$ নির্ণয় কর। (পানির আপেক্ষিক তাপ $c = 4200\text{ J/kg}\cdot\text{K}$)।</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>##PRESET:heat-engine[size:medium]##</t>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 23)।</t>
+          <t>তাপমাত্রা পরিবর্তনশীল প্রক্রিয়ায় এন্ট্রপির পরিবর্তন $\Delta S = \int_{T_1}^{T_2} \frac{mc dT}{T} = m c \ln\left(\frac{T_2}{T_1}\right)$। $T_1 = 273.15\text{ K}$, $T_2 = 373.15\text{ K}$। $\Delta S = 1.0 \times 4200 \times \ln\left(\frac{373.15}{273.15}\right) = 4200 \times \ln(1.3661) = 4200 \times 0.31195 \approx 1310.2\text{ J/K}$।</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 23</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>এন্ট্রপির পরিবর্তন $\Delta S = 1310.2\text{ J/K}$</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4864,12 +4593,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>রেফ্রিজারেটরের কার্যসম্পাদন গুণক (COP) (সমস্যা 24)</t>
+          <t>এন্ট্রপি পরিবর্তন, সুপ্ততাপ ও ২য় সূত্র (Entropy Changes &amp; 2nd Law)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -4877,25 +4606,25 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[সমস্যা 24: রেফ্রিজারেটরের কার্যসম্পাদন গুণক (COP)]
-একটি আদর্শ রেফ্রিজারেটর $T_2 = -2^\circ\text{C}$ তাপমাত্রা হতে তাপ শোষণ করে $T_1 = 27^\circ\text{C}$ তাপমাত্রার বায়ুমণ্ডলে তাপ বর্জন করে। রেফ্রিজারেটরটির কার্যসম্পাদন সহগ বা গুণক ($COP = \frac{T_2}{T_1 - T_2}$) কত?</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2.5,h=3.5][size:small]##
+একটি তাপীয় অন্তরিত পাত্রে $10^\circ\text{C}$ তাপমাত্রার $2.0\text{ kg}$ পানির সাথে $80^\circ\text{C}$ তাপমাত্রার $3.0\text{ kg}$ পানি মিশ্রিত করা হলো। মিশ্রণের চূড়ান্ত তাপমাত্রা এবং এই অপ্রত্যাবর্তী মিশ্রণ প্রক্রিয়ায় মোট এন্ট্রপির নিট বৃদ্ধি (এন্ট্রপি সৃষ্টি) নির্ণয় কর। ($c = 4200\text{ J/kg}\cdot\text{K}$)।</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2.5,h=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 24)।</t>
+          <t>তাপ গ্রহণ = তাপ বর্জন: $m_1 c (T_f - T_1) = m_2 c (T_2 - T_f) \implies 2(T_f - 10) = 3(80 - T_f) \implies 2T_f - 20 = 240 - 3T_f \implies 5T_f = 260 \implies T_f = 52.0^\circ\text{C} = 325.15\text{ K}$। $T_1 = 283.15\text{ K}, T_2 = 353.15\text{ K}$। শীতল পানির এন্ট্রপি পরিবর্তন $\Delta S_1 = 2(4200)\ln(325.15/283.15) = 8400 \times 0.1383 = +1161.7\text{ J/K}$। উষ্ণ পানির $\Delta S_2 = 3(4200)\ln(325.15/353.15) = 12600 \times (-0.08257) = -1040.4\text{ J/K}$। নিট পরিবর্তন $\Delta S_{\text{total}} = 1161.7 - 1040.4 = +121.3\text{ J/K} &gt; 0$।</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 24</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>মিশ্রণের চূড়ান্ত তাপমাত্রা $T_f = 52.0^\circ\text{C} = 325.15\text{ K}$, এন্ট্রপির বৃদ্ধি $\Delta S_{\text{net}} = 38.45\text{ J/K}$</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4915,38 +4644,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>সমোষ্ণ প্রক্রিয়ায় কৃতকাজ ও তাপ (সমস্যা 25)</t>
+          <t>এন্ট্রপি পরিবর্তন, সুপ্ততাপ ও ২য় সূত্র (Entropy Changes &amp; 2nd Law)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[সমস্যা 25: সমোষ্ণ প্রক্রিয়ায় কৃতকাজ ও তাপ]
-$V_1 = 1.0\text{ L}$ আয়তনের একটি আদর্শ গ্যাসকে স্থির তাপমাত্রা $T = 400\text{ K}$-এ সমোষ্ণ প্রক্রিয়ায় প্রসারিত করে আয়তন $V_2 = 1.0\text{ L}$ করা হলো। গ্যাসে প্রদত্ত তাপশক্তি ও কৃতকাজ $W = nRT \ln(V_2/V_1)$ কত? ($n = 1\text{ mol}$)</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি আদর্শ গ্যাসের $1.0\text{ মোল}$ গ্যাসকে সমোষ্ণভাবে প্রসারিত করে আদি আয়তনের দ্বিগুণ করা হলো। গ্যাসটির এন্ট্রপির পরিবর্তন কত? ($R = 8.314\text{ J/mol}\cdot\text{K}$)।</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 25)।</t>
+          <t>সমোষ্ণ প্রসারণে $\Delta U = 0 \implies Q = W = nRT \ln(V_2/V_1)$। এন্ট্রপির পরিবর্তন $\Delta S = \frac{Q}{T} = n R \ln(V_2/V_1) = 1.0 \times 8.314 \times \ln(2) = 8.314 \times 0.69315 \approx 5.763\text{ J/K}$।</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 25</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>এন্ট্রপির পরিবর্তন $\Delta S = 5.76\text{ J/K}$</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4966,12 +4695,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>পানি বাষ্পীভবনে এন্ট্রপি বৃদ্ধি (সমস্যা 26)</t>
+          <t>এন্ট্রপি পরিবর্তন, সুপ্ততাপ ও ২য় সূত্র (Entropy Changes &amp; 2nd Law)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -4979,25 +4708,25 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[সমস্যা 26: পানি বাষ্পীভবনে এন্ট্রপি বৃদ্ধি]
-$100^\circ\text{C}$ তাপমাত্রার $600\text{ g}$ পানিকে ফুটন্ত অবস্থায় সম-তাপমাত্রার বাষ্পে পরিণত করা হলো। এই প্রক্রিয়ায় এন্ট্রপির পরিবর্তন কত? (বাষ্পীভবনের সুপ্ততাপ $L_v = 2.26 \times 10^6\text{ J/kg}$)</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+রুদ্ধতাপীয় প্রত্যাবর্তী প্রক্রিয়ায় (Isentropic process) কোনো সিস্টেমের এন্ট্রপির পরিবর্তন কত এবং কেন রুদ্ধতাপীয় রেখাকে আইসোএনট্রপিক রেখা বলা হয়?</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 26)।</t>
+          <t>রুদ্ধতাপীয় প্রক্রিয়ায় সিস্টেমের ভেতর বা বাইরে কোনো তাপ প্রবেশ বা নির্গত হয় না: $dQ = 0$। ফলে এন্ট্রপির পরিবর্তন $dS = \frac{dQ}{T} = 0 \implies S = \text{ধ্রুবক}$। এই কারণে প্রত্যাবর্তী রুদ্ধতাপীয় রেখাকে সম-এন্ট্রপি রেখা বা আইসোএনট্রপিক (Isentropic) রেখা বলা হয়।</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 26</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>এন্ট্রপির পরিবর্তন $\Delta S = 0$, প্রক্রিয়াটিতে তাপের আদান-প্রদান না থাকায় এন্ট্রপি ধ্রুব থাকে</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5017,38 +4746,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম সূত্র ও অভ্যন্তরীণ শক্তি (সমস্যা 27)</t>
+          <t>এন্ট্রপি পরিবর্তন, সুপ্ততাপ ও ২য় সূত্র (Entropy Changes &amp; 2nd Law)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[সমস্যা 27: তাপগতিবিদ্যার ১ম সূত্র ও অভ্যন্তরীণ শক্তি]
-একটি আবদ্ধ গ্যাস ব্যবস্থায় বাইরে হতে $\Delta Q = 850\text{ J}$ তাপশক্তি সরবরাহ করা হলো এবং ব্যবস্থাটি সম্প্রসারিত হয়ে $\Delta W = 500\text{ J}$ কাজ সম্পাদন করল। ব্যবস্থার অভ্যন্তরীণ শক্তির পরিবর্তন $\Delta U = \Delta Q - \Delta W$ কত?</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+$-10^\circ\text{C}$ তাপমাত্রার $50\text{ g}$ বরফকে $0^\circ\text{C}$ তাপমাত্রার পানিতে রূপান্তর করতে মোট এন্ট্রপির পরিবর্তন কত? (বরফের আপেক্ষিক তাপ $s_{	ext{ice}} = 2100\text{ J/kg}\cdot\text{K}$, $L_f = 3.36 \times 10^5\text{ J/kg}$)।</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 27)।</t>
+          <t>১ম ধাপ (বরফ $-10^\circ\text{C}$ হতে $0^\circ\text{C}$): $\Delta S_1 = m s_{\text{ice}} \ln(T_2/T_1) = 0.05 \times 2100 \times \ln(273.15/263.15) = 105 \times \ln(1.038) = 105 \times 0.0373 \approx 3.917\text{ J/K}$। ২য় ধাপ (বরফ গলন): $\Delta S_2 = \frac{m L_f}{T_2} = \frac{0.05 \times 3.36 \times 10^5}{273.15} = \frac{16800}{273.15} \approx 61.505\text{ J/K}$। মোট পরিবর্তন $\Delta S = 3.917 + 61.505 = 65.42\text{ J/K}$।</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 27</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>মোট এন্ট্রপির পরিবর্তন $\Delta S = 65.41\text{ J/K}$</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5068,12 +4797,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>দ্বি-পরমাণুক গ্যাসের গামা ও রূদ্ধতাপীয় সমীকরণ (সমস্যা 28)</t>
+          <t>এন্ট্রপি পরিবর্তন, সুপ্ততাপ ও ২য় সূত্র (Entropy Changes &amp; 2nd Law)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -5081,25 +4810,25 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[সমস্যা 28: দ্বি-পরমাণুক গ্যাসের গামা ও রূদ্ধতাপীয় সমীকরণ]
-একটি দ্বি-পরমাণুক গ্যাসের জন্য $\gamma = 1.4$। গ্যাসটির প্রারম্ভিক চাপ $P_1 = 1\text{ atm}$ এবং আয়তন $V_1$ হতে রূদ্ধতাপীয় প্রক্রিয়ায় আয়তন সংকুচিত করে এক-চতুর্থাংশ ($V_2 = V_1 / 4$) করা হলে চূড়ান্ত চাপ $P_2 = P_1 (V_1/V_2)^\gamma$ কত অ্যাটমস্ফিয়ার হবে?</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি প্রত্যাবর্তী কার্নো চক্রের এন্ট্রপি-তাপমাত্রা ($T-S$) চিত্রে একটি আয়তক্ষেত্র উৎপন্ন হয় যার প্রস্থ $\Delta S = 200\text{ J/K}$ এবং তাপমাত্রা সীমা যথাক্রমে $600\text{ K}$ ও $300\text{ K}$। প্রতি চক্রে কৃতকাজ এবং গৃহীত তাপ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 28)।</t>
+          <t>$T-S$ চিত্রে গৃহীত তাপ হলো শীর্ষ রেখার নিচের ক্ষেত্রফল: $Q_1 = T_1 \Delta S = 600 \times 200 = 120000\text{ J} = 120.0\text{ kJ}$। বর্জিত তাপ $Q_2 = T_2 \Delta S = 300 \times 200 = 60000\text{ J} = 60.0\text{ kJ}$। প্রতি চক্রে কৃতকাজ হলো আয়তক্ষেত্রের ক্ষেত্রফল: $W = (T_1 - T_2)\Delta S = (600 - 300) \times 200 = 60000\text{ J} = 60.0\text{ kJ}$।</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 28</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>গৃহীত তাপ $Q_1 = 120.0\text{ kJ}$, কৃতকাজ $W = 60.0\text{ kJ}$</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5119,38 +4848,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>কার্নো ইঞ্জিনের গ্রাহকের তাপমাত্রা পরিবর্তন (সমস্যা 29)</t>
+          <t>এন্ট্রপি পরিবর্তন, সুপ্ততাপ ও ২য় সূত্র (Entropy Changes &amp; 2nd Law)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[সমস্যা 29: কার্নো ইঞ্জিনের গ্রাহকের তাপমাত্রা পরিবর্তন]
-একটি কার্নো ইঞ্জিনের বর্তমান দক্ষতা $120\%$। তাপগ্রাহকের তাপমাত্রা $90\text{ K}$ হ্রাস করলে ইঞ্জিনের নতুন দক্ষতা কত বৃদ্ধি পাবে, যদি উৎসের তাপমাত্রা $T_1 = 600\text{ K}$ স্থির থাকে?</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+মহাবিশ্বের এন্ট্রপি সংক্রান্ত ক্লসিয়াসের অমর উক্তি: 'মহাবিশ্বের শক্তি নির্দিষ্ট কিন্তু এন্ট্রপি ক্রমাগত বৃদ্ধি পাচ্ছে'—উক্তিটির ভৌত তাৎপর্য এবং তাপীয় মৃত্যু (Thermal death of universe) ধারণাটি ব্যাখ্যা কর।</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 29)।</t>
+          <t>শক্তি সংরক্ষিত থাকলেও কাজের জন্য উপযোগী মুক্ত শক্তি হ্রাস পায় এবং অনুপযোগী তাপ শক্তিতে রূপান্তরিত হয়। মহাবিশ্বের সকল অপ্রত্যাবর্তী প্রক্রিয়ায় এন্ট্রপি বৃদ্ধি পায় ($\Delta S &gt; 0$)। একসময় যখন সমগ্র মহাবিশ্ব একটি অভিন্ন সমতাপমাত্রায় পৌঁছাবে, তখন কোনো তাপ ইঞ্জিন কাজ করতে পারবে না এবং কোনো শক্তি রূপান্তর সম্ভব হবে না—একে মহাবিশ্বের তাপীয় মৃত্যু বলা হয়।</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 29</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>সকল স্বতঃস্ফূর্ত প্রাকৃতিক প্রক্রিয়া অপ্রত্যাবর্তী হওয়ায় $\Delta S_{\text{univ}} &gt; 0$; চূড়ান্ত অবস্থায় তাপীয় ভারসাম্য ও কার্যকর কাজের ক্ষমতা বিলুপ্ত হবে</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5170,12 +4899,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>থার্মোমিটারের মৌলিক ব্যবধান ও পরম শূন্য (সমস্যা 30)</t>
+          <t>এন্ট্রপি পরিবর্তন, সুপ্ততাপ ও ২য় সূত্র (Entropy Changes &amp; 2nd Law)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -5183,25 +4912,25 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[সমস্যা 30: থার্মোমিটারের মৌলিক ব্যবধান ও পরম শূন্য]
-একটি ত্রুটিপূর্ণ থার্মোমিটার গলিত বরফে $2^\circ\text{C}$ এবং প্রমাণ চাপে বাষ্পে $91^\circ\text{C}$ পাঠ প্রদর্শন করে। থার্মোমিটারটি $50^\circ\text{C}$ পাঠ দিলে ফারেনহাইট স্কেলে এর সঠিক মান কত?</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি আদর্শ গ্যাসকে মুক্ত প্রসারণে (Free expansion / Joule expansion) অন্তরিত আধারে প্রসারিত হতে দেওয়া হলো। এই প্রক্রিয়ায় অভ্যন্তরীণ শক্তি পরিবর্তন, কৃতকাজ এবং এন্ট্রপির পরিবর্তন কীরূপ হবে?</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 30)।</t>
+          <t>মুক্ত প্রসারণে কোনো বাহ্যিক বলের বিরুদ্ধে কাজ হয় না ($W = 0$) এবং তাপ আদান-প্রদান নেই ($Q = 0$)। ১ম সূত্র মতে $\Delta U = 0 \implies \Delta T = 0$। তবে প্রক্রিয়াটি অত্যন্ত অপ্রত্যাবর্তী ও স্বতঃস্ফূর্ত হওয়ায় অণুগুলোর বিশৃঙ্খলা বৃদ্ধি পায় এবং এন্ট্রপির নিট বৃদ্ধি ঘটে: $\Delta S = n R \ln(V_2/V_1) &gt; 0$।</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 30</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>$W = 0, \Delta U = 0, \Delta T = 0$ (তাপমাত্রা অপরিবর্তিত), কিন্তু $\Delta S = n R \ln(V_2/V_1) &gt; 0$ (এন্ট্রপি বৃদ্ধি পায়)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5221,44 +4950,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>কার্নো চক্র ও সর্বোচ্চ কর্মদক্ষতা (সমস্যা 31)</t>
+          <t>বাস্তব ইঞ্জিন চক্র ও সূচক চিত্র (Real Cycles &amp; Indicator Diagrams)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>##PRESET:carnot-cycle[size:medium]##
-[সমস্যা 31: কার্নো চক্র ও সর্বোচ্চ কর্মদক্ষতা]
-##PRESET:carnot-cycle[size:medium]##
-একটি কার্নো ইঞ্জিন $T_1 = 400\text{ K}$ তাপমাত্রার তাপ উৎস হতে $Q_1 = 3000\text{ J}$ তাপ গ্রহণ করে এবং $T_2 = 300\text{ K}$ তাপমাত্রার গ্রাহকে তাপ বর্জন করে। ইঞ্জিনটির কর্মদক্ষতা ($\ eta = 1 - T_2/T_1$) এবং প্রতি চক্রে সম্পাদিত কাজের মান কত?</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি গ্যাসকে তিনটি ধাপে চক্রাকারে ঘুরানো হলো: (১) সমোষ্ণ প্রসারণ $A 	o B$ ($T = 400\text{ K}$)-এ আয়তন দ্বিগুণ হয় ($V_B = 2V_A$), (২) স্থির চাপে সংকোচন $B 	o C$ ($V_C = V_A$), (৩) স্থির আয়তনে উত্তাপন $C 	o A$। ১ মোল আদর্শ গ্যাসের ক্ষেত্রে পুরো চক্রে নেট কাজ $W_{\text{net}}$ নির্ণয় কর। ($R = 8.314\text{ J/mol}\cdot\text{K}$)।</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>##PRESET:carnot-cycle[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 31)।</t>
+          <t>ধাপ ১ ($A \to B$): $W_1 = n R T \ln(V_B/V_A) = 1.0 \times 8.314 \times 400 \times \ln(2) = 3325.6 \times 0.69315 \approx 2305.1\text{ J}$। ধাপ ২ ($B \to C$ সমচাপ সংকোচন): $P_B = \frac{nRT}{2V_A}$। $W_2 = P_B (V_C - V_B) = \frac{nRT}{2V_A}(V_A - 2V_A) = -\frac{1}{2}nRT = -0.5(3325.6) = -1662.8\text{ J}$। ধাপ ৩ ($C \to A$ সমআয়তন): $W_3 = 0$। মোট কাজ $W_{\text{net}} = 2305.1 - 1662.8 = 642.3\text{ J}$।</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 31</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>নেট কাজ $W_{\text{net}} = 642.5\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5278,12 +5001,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>বরফ গলন ও তাপমাত্রা বৃদ্ধিতে এন্ট্রপি (সমস্যা 32)</t>
+          <t>বাস্তব ইঞ্জিন চক্র ও সূচক চিত্র (Real Cycles &amp; Indicator Diagrams)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -5291,25 +5014,25 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[সমস্যা 32: বরফ গলন ও তাপমাত্রা বৃদ্ধিতে এন্ট্রপি]
-$0^\circ\text{C}$ তাপমাত্রার $60\text{ g}$ বরফকে $50^\circ\text{C}$ তাপমাত্রার পানিতে রূপান্তরিত করা হলো। এই সামগ্রিক প্রক্রিয়ায় মোট এন্ট্রপির পরিবর্তন ($\Delta S$) কত জুল/কেলভিন? ($L_f = 3.36 \times 10^5\text{ J/kg}, s = 4200\text{ J/(kg}\cdot\text{K)}$)</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##
+একটি পেট্রোল ইঞ্জিনের অটো চক্রের (Otto cycle) সংকোচন অনুপাত $r = V_1/V_2 = 8$। কার্যকরী গ্যাস হিসেবে বায়ুকে ধরে ($\gamma = 1.4$) অটো চক্রের তাত্ত্বিক দক্ষতা $\eta = 1 - rac{1}{r^{\gamma-1}}$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 32)।</t>
+          <t>অটো চক্রের দক্ষতা $\eta = 1 - \frac{1}{r^{\gamma - 1}} = 1 - \frac{1}{8^{1.4 - 1}} = 1 - \frac{1}{8^{0.4}}$। $8^{0.4} = (2^3)^{0.4} = 2^{1.2} \approx 2.2974$। $\eta = 1 - \frac{1}{2.2974} = 1 - 0.43528 = 0.56472 = 56.47\%$।</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 32</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>তাত্ত্বিক দক্ষতা $\eta = 56.47\%$</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5329,44 +5052,39 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>রূদ্ধতাপীয় প্রসারণ ও কাজের হিসাব (সমস্যা 33)</t>
+          <t>বাস্তব ইঞ্জিন চক্র ও সূচক চিত্র (Real Cycles &amp; Indicator Diagrams)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>##PRESET:heat-engine[size:medium]##
-[সমস্যা 33: রূদ্ধতাপীয় প্রসারণ ও কাজের হিসাব]
-##PRESET:heat-engine[size:medium]##
-$1\text{ mol}$ হিলিয়াম গ্যাস ($C_v = 1.5R$) প্রারম্ভিক তাপমাত্রা $T_1 = 800\text{ K}$ হতে রূদ্ধতাপীয় প্রক্রিয়ায় প্রসারিত হয়ে তাপমাত্রা $T_2 = 700\text{ K}$-এ নেমে এলো। গ্যাস কর্তৃক সম্পাদিত কাজের মান $W = n C_v(T_1 - T_2)$ কত জুল? ($R = 8.314\text{ J/(mol}\cdot\text{K)}$)</t>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##
+একটি ডিজেল ইঞ্জিনের সংকোচন অনুপাত $r = 16$ এবং জ্বালানি কাটিং অনুপাত $r_c = 2$। $\gamma = 1.4$ ধরে ডিজেল চক্রের তাত্ত্বিক দক্ষতা $\eta = 1 - rac{1}{\gamma r^{\gamma-1}}\left[rac{r_c^\gamma - 1}{r_c - 1}+ight]$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>##PRESET:heat-engine[size:medium]##</t>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 33)।</t>
+          <t>$r^{\gamma-1} = 16^{0.4} = (2^4)^{0.4} = 2^{1.6} \approx 3.0314$। $\frac{r_c^\gamma - 1}{r_c - 1} = \frac{2^{1.4} - 1}{2 - 1} = 2.639 - 1 = 1.639$। পদটি $= \frac{1.639}{1.4 \times 3.0314} = \frac{1.639}{4.244} \approx 0.3862$। দক্ষতা $\eta = 1 - 0.3862 = 0.6138 = 61.38\%$।</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 33</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>তাত্ত্বিক দক্ষতা $\eta = 61.38\%$</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5386,12 +5104,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>রেফ্রিজারেটরের কার্যসম্পাদন গুণক (COP) (সমস্যা 34)</t>
+          <t>বাস্তব ইঞ্জিন চক্র ও সূচক চিত্র (Real Cycles &amp; Indicator Diagrams)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -5399,25 +5117,25 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[সমস্যা 34: রেফ্রিজারেটরের কার্যসম্পাদন গুণক (COP)]
-একটি আদর্শ রেফ্রিজারেটর $T_2 = -10^\circ\text{C}$ তাপমাত্রা হতে তাপ শোষণ করে $T_1 = 27^\circ\text{C}$ তাপমাত্রার বায়ুমণ্ডলে তাপ বর্জন করে। রেফ্রিজারেটরটির কার্যসম্পাদন সহগ বা গুণক ($COP = \frac{T_2}{T_1 - T_2}$) কত?</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি আদর্শ গ্যাসকে প্রাথমিক চাপ $P_0$ হতে দুইভাবে অর্ধেক আয়তনে ($V_0/2$) সংকুচিত করা হলো: প্রথমত সমোষ্ণভাবে এবং দ্বিতীয়ত রুদ্ধতাপীয়ভাবে। কোন ক্ষেত্রে গ্যাসের ওপর বেশি কাজ করতে হবে এবং কেন? গ্রাফ এঁকে ব্যাখ্যা কর।</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 34)।</t>
+          <t>$P-V$ লেখচিত্রে রুদ্ধতাপীয় রেখা সমোষ্ণ রেখার চেয়ে $\gamma$ গুণ খাড়া হওয়ায় রুদ্ধতাপীয় সংকোচনের বক্ররেখাটি সমোষ্ণ রেখার ওপরে অবস্থান করে। ফলে রুদ্ধতাপীয় সংকোচন বক্ররেখার নিচের ক্ষেত্রফল সমোষ্ণ রেখার নিচের ক্ষেত্রফলের চেয়ে বেশি হয়, অর্থাৎ গ্যাসের ওপর কৃতকাজ বেশি করতে হয়।</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 34</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>রুদ্ধতাপীয় সংকোচনে বেশি কাজ সম্পাদিত হবে ($|W_{\text{adi}}| &gt; |W_{\text{iso}}|$)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5437,38 +5155,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>সমোষ্ণ প্রক্রিয়ায় কৃতকাজ ও তাপ (সমস্যা 35)</t>
+          <t>বাস্তব ইঞ্জিন চক্র ও সূচক চিত্র (Real Cycles &amp; Indicator Diagrams)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[সমস্যা 35: সমোষ্ণ প্রক্রিয়ায় কৃতকাজ ও তাপ]
-$V_1 = 1.0\text{ L}$ আয়তনের একটি আদর্শ গ্যাসকে স্থির তাপমাত্রা $T = 1200\text{ K}$-এ সমোষ্ণ প্রক্রিয়ায় প্রসারিত করে আয়তন $V_2 = 1.0\text{ L}$ করা হলো। গ্যাসে প্রদত্ত তাপশক্তি ও কৃতকাজ $W = nRT \ln(V_2/V_1)$ কত? ($n = 1\text{ mol}$)</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি পাত্রে $27^\circ\text{C}$ তাপমাত্রায় এবং $10^5\text{ Pa}$ চাপে হিলিয়াম গ্যাস রয়েছে। গ্যাসটিকে রুদ্ধতাপীয়ভাবে হঠাৎ সংকুচিত করে আয়তন এক-চতুর্থাংশ ($V/4$) করা হলো। গ্যাসের অন্তিম চাপ ও তাপমাত্রা কত? ($\gamma = 5/3$)।</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 35)।</t>
+          <t>$P_2 = P_1 (V_1/V_2)^\gamma = 10^5 \times 4^{5/3} = 10^5 \times (4^{1.667}) = 10^5 \times 10.079 = 1.0079 \times 10^6\text{ Pa}$। তাপমাত্রা $T_2 = T_1 (V_1/V_2)^{\gamma-1} = 300 \times 4^{2/3} = 300 \times 2.5198 \approx 755.95\text{ K}$। সেলসিয়াসে $\theta_2 = 755.95 - 273.15 = 482.8^\circ\text{C}$।</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 35</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>অন্তিম চাপ $P_2 = 1.008 \times 10^6\text{ Pa} \approx 10.08\text{ atm}$, অন্তিম তাপমাত্রা $T_2 = 755.95\text{ K} = 482.8^\circ\text{C}$</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5488,12 +5206,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>পানি বাষ্পীভবনে এন্ট্রপি বৃদ্ধি (সমস্যা 36)</t>
+          <t>বাস্তব ইঞ্জিন চক্র ও সূচক চিত্র (Real Cycles &amp; Indicator Diagrams)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -5501,25 +5219,25 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[সমস্যা 36: পানি বাষ্পীভবনে এন্ট্রপি বৃদ্ধি]
-$100^\circ\text{C}$ তাপমাত্রার $200\text{ g}$ পানিকে ফুটন্ত অবস্থায় সম-তাপমাত্রার বাষ্পে পরিণত করা হলো। এই প্রক্রিয়ায় এন্ট্রপির পরিবর্তন কত? (বাষ্পীভবনের সুপ্ততাপ $L_v = 2.26 \times 10^6\text{ J/kg}$)</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি তাপ ইঞ্জিন প্রতিটি চক্রে $Q_1 = 5000\text{ J}$ তাপ গ্রহণ করে এবং $W = 1500\text{ J}$ কাজ করে। ইঞ্জিনটির নির্গত তাপ $Q_2$ কত? যদি তাপ আধারের তাপমাত্রা যথাক্রমে $800\text{ K}$ ও $400\text{ K}$ হয়, তবে ইঞ্জিনটি কি আদর্শ কার্নো ইঞ্জিন নাকি অপ্রত্যাবর্তী বাস্তব ইঞ্জিন?</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 36)।</t>
+          <t>বর্জিত তাপ $Q_2 = Q_1 - W = 5000 - 1500 = 3500\text{ J}$। ইঞ্জিনের কার্যকর দক্ষতা $\eta = \frac{W}{Q_1} = \frac{1500}{5000} = 0.30 = 30\%$। কিন্তু এই তাপমাত্রার মধ্যে তাত্ত্বিক কার্নো দক্ষতা $\eta_C = 1 - \frac{400}{800} = 0.50 = 50\%$। যেহেতু $\eta &lt; \eta_C$, তাই এটি একটি বাস্তব অপ্রত্যাবর্তী ইঞ্জিন।</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 36</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>বর্জিত তাপ $Q_2 = 3500\text{ J}$, ইঞ্জিনটি অপ্রত্যাবর্তী বাস্তব ইঞ্জিন ($\eta = 30\% &lt; \eta_{\text{Carnot}} = 50\%$)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5539,38 +5257,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম সূত্র ও অভ্যন্তরীণ শক্তি (সমস্যা 37)</t>
+          <t>বাস্তব ইঞ্জিন চক্র ও সূচক চিত্র (Real Cycles &amp; Indicator Diagrams)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[সমস্যা 37: তাপগতিবিদ্যার ১ম সূত্র ও অভ্যন্তরীণ শক্তি]
-একটি আবদ্ধ গ্যাস ব্যবস্থায় বাইরে হতে $\Delta Q = 450\text{ J}$ তাপশক্তি সরবরাহ করা হলো এবং ব্যবস্থাটি সম্প্রসারিত হয়ে $\Delta W = 500\text{ J}$ কাজ সম্পাদন করল। ব্যবস্থার অভ্যন্তরীণ শক্তির পরিবর্তন $\Delta U = \Delta Q - \Delta W$ কত?</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি পিস্টনযুক্ত সিলিন্ডারে রক্ষিত আদর্শ গ্যাসের অভ্যন্তরীণ শক্তি বৃদ্ধির রাশিমালা $\Delta U = n C_v \Delta T$ যে কেবল সমআয়তন প্রক্রিয়াতেই নয় বরং যেকোনো সাধারণ তাপগতীয় প্রক্রিয়াতেই সত্য—তা প্রমাণ কর।</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 37)।</t>
+          <t>জুলের সূত্রানুসারে আদর্শ গ্যাসের অভ্যন্তরীণ শক্তি কেবল তাপমাত্রার অপেক্ষক $U = U(T)$। যেকোনো প্রক্রিয়ায় প্রারম্ভিক তাপমাত্রা $T_1$ এবং অন্তিম তাপমাত্রা $T_2$ হলে অভ্যন্তরীণ শক্তির পরিবর্তন $\Delta U = \int_{T_1}^{T_2} n C_v dT = n C_v \Delta T$ প্রক্রিয়ার গতিপথের ওপর নির্ভর করে না।</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 37</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>অভ্যন্তরীণ শক্তি একটি অবস্থা অপেক্ষক (State function) যা কেবলমাত্র তাপমাত্রার ওপর নির্ভর করে</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5590,12 +5308,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>দ্বি-পরমাণুক গ্যাসের গামা ও রূদ্ধতাপীয় সমীকরণ (সমস্যা 38)</t>
+          <t>বাস্তব ইঞ্জিন চক্র ও সূচক চিত্র (Real Cycles &amp; Indicator Diagrams)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -5603,25 +5321,25 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[সমস্যা 38: দ্বি-পরমাণুক গ্যাসের গামা ও রূদ্ধতাপীয় সমীকরণ]
-একটি দ্বি-পরমাণুক গ্যাসের জন্য $\gamma = 1.4$। গ্যাসটির প্রারম্ভিক চাপ $P_1 = 1\text{ atm}$ এবং আয়তন $V_1$ হতে রূদ্ধতাপীয় প্রক্রিয়ায় আয়তন সংকুচিত করে এক-চতুর্থাংশ ($V_2 = V_1 / 4$) করা হলে চূড়ান্ত চাপ $P_2 = P_1 (V_1/V_2)^\gamma$ কত অ্যাটমস্ফিয়ার হবে?</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি বদ্ধ তাপগতীয় চক্রে ক্লসিয়াসের উপপাদ্য $\oint rac{dQ}{T} \le 0$ অনুসারে প্রত্যাবর্তী চক্রে এর মান কত এবং অপ্রত্যাবর্তী চক্রে এর মান কত হয়?</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 38)।</t>
+          <t>প্রত্যাবর্তী চক্রে এন্ট্রপি একটি অবস্থা অপেক্ষক হওয়ায় পূর্ণ চক্র শেষে মোট এন্ট্রপি পরিবর্তন শূন্য হয় ($\oint dS = \oint \frac{dQ_{\text{rev}}}{T} = 0$)। কিন্তু যেকোনো অপ্রত্যাবর্তী চক্রে অভ্যন্তরীণ অপচয় বা ঘর্ষণের কারণে $\oint \frac{dQ}{T} &lt; 0$ হয়।</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 38</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>প্রত্যাবর্তী চক্রে $\oint \frac{dQ}{T} = 0$, অপ্রত্যাবর্তী চক্রে $\oint \frac{dQ}{T} &lt; 0$</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5641,38 +5359,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>কার্নো ইঞ্জিনের গ্রাহকের তাপমাত্রা পরিবর্তন (সমস্যা 39)</t>
+          <t>বাস্তব ইঞ্জিন চক্র ও সূচক চিত্র (Real Cycles &amp; Indicator Diagrams)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[সমস্যা 39: কার্নো ইঞ্জিনের গ্রাহকের তাপমাত্রা পরিবর্তন]
-একটি কার্নো ইঞ্জিনের বর্তমান দক্ষতা $80\%$। তাপগ্রাহকের তাপমাত্রা $90\text{ K}$ হ্রাস করলে ইঞ্জিনের নতুন দক্ষতা কত বৃদ্ধি পাবে, যদি উৎসের তাপমাত্রা $T_1 = 600\text{ K}$ স্থির থাকে?</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি রেফ্রিজারেটর প্রতি সেকেন্ডে $250\text{ W}$ বৈদ্যুতিক শক্তি গ্রহণ করে ফ্রিজার হতে বরফ তৈরির জন্য তাপ অপসারণ করে। ফ্রিজারের তাপমাত্রা $-10^\circ\text{C}$ এবং ঘরের তাপমাত্রা $25^\circ\text{C}$ হলে তাত্ত্বিকভাবে প্রতি মিনিটে সর্বোচ্চ কত কেজি $0^\circ\text{C}$ তাপমাত্রার পানিকে $0^\circ\text{C}$ তাপমাত্রার বরফে পরিণত করা সম্ভব? ($L_f = 3.36 \times 10^5\text{ J/kg}$)।</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 39)।</t>
+          <t>তাত্ত্বিক $\text{COP} \beta = \frac{T_2}{T_1 - T_2} = \frac{263.15}{298.15 - 263.15} = \frac{263.15}{35} \approx 7.5186$। প্রতি সেকেন্ডে অপসারিত সর্বোচ্চ তাপ $Q_2 = \beta W = 7.5186 \times 250\text{ W} = 1879.64\text{ J/s}$। প্রতি মিনিটে অপসারিত তাপ $Q_{\text{min}} = 1879.64 \times 60 = 112778.6\text{ J}$। বরফ রূপান্তর: $m = \frac{Q_{\text{min}}}{L_f} = \frac{112778.6}{336000} \approx 0.3356\text{ kg/min} \approx 335.6\text{ g/min}$।</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 39</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>সর্বোচ্চ বরফ উৎপাদন হার $m = 0.335\text{ kg/min} \approx 335.2\text{ g/min}$</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5692,12 +5410,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>থার্মোমিটারের মৌলিক ব্যবধান ও পরম শূন্য (সমস্যা 40)</t>
+          <t>বাস্তব ইঞ্জিন চক্র ও সূচক চিত্র (Real Cycles &amp; Indicator Diagrams)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -5705,25 +5423,25 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[সমস্যা 40: থার্মোমিটারের মৌলিক ব্যবধান ও পরম শূন্য]
-একটি ত্রুটিপূর্ণ থার্মোমিটার গলিত বরফে $10^\circ\text{C}$ এবং প্রমাণ চাপে বাষ্পে $91^\circ\text{C}$ পাঠ প্রদর্শন করে। থার্মোমিটারটি $50^\circ\text{C}$ পাঠ দিলে ফারেনহাইট স্কেলে এর সঠিক মান কত?</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি গ্যাস সমচাপ প্রক্রিয়ায় প্রসারিত হয়ে আদি আয়তনের দ্বিগুণ হলে সরবরাহকৃত তাপের কত শতাংশ অভ্যন্তরীণ শক্তি বৃদ্ধিতে এবং কত শতাংশ বাহ্যিক কাজে ব্যয় হয়? ($\gamma = 1.4$ বিশিষ্ট দ্বিপরমাণুক গ্যাস)।</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 40)।</t>
+          <t>সরবরাহকৃত তাপ $Q = n C_p \Delta T$। অভ্যন্তরীণ শক্তি বৃদ্ধি $\Delta U = n C_v \Delta T$। বাহ্যিক কাজ $W = n R \Delta T = Q - \Delta U$। অভ্যন্তরীণ শক্তিতে ব্যয়ের ভগ্নাংশ $= \frac{\Delta U}{Q} = \frac{C_v}{C_p} = \frac{1}{\gamma} = \frac{1}{1.40} \approx 0.7143 = 71.43\%$। বাহ্যিক কাজে ব্যয়ের ভগ্নাংশ $= \frac{W}{Q} = 1 - \frac{1}{\gamma} = 1 - 0.7143 = 0.2857 = 28.57\%$।</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 40</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>অভ্যন্তরীণ শক্তিতে ব্যয় $= 71.43\%$, বাহ্যিক কাজে ব্যয় $= 28.57\%$</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5743,44 +5461,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>কার্নো চক্র ও সর্বোচ্চ কর্মদক্ষতা (সমস্যা 41)</t>
+          <t>উন্নত তাপগতীয় সংশ্লেষণ ও তাত্ত্বিক বিশ্লেষণ (Advanced Thermodynamics)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>##PRESET:carnot-cycle[size:medium]##
-[সমস্যা 41: কার্নো চক্র ও সর্বোচ্চ কর্মদক্ষতা]
-##PRESET:carnot-cycle[size:medium]##
-একটি কার্নো ইঞ্জিন $T_1 = 1200\text{ K}$ তাপমাত্রার তাপ উৎস হতে $Q_1 = 3000\text{ J}$ তাপ গ্রহণ করে এবং $T_2 = 300\text{ K}$ তাপমাত্রার গ্রাহকে তাপ বর্জন করে। ইঞ্জিনটির কর্মদক্ষতা ($\ eta = 1 - T_2/T_1$) এবং প্রতি চক্রে সম্পাদিত কাজের মান কত?</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি সিলিন্ডারে $n$ মোল গ্যাসকে একটি সরলরেখা বরাবর $A(P_0, V_0)$ অবস্থা হতে $B(2P_0, 2V_0)$ অবস্থায় প্রসারিত করা হলো। এই প্রক্রিয়ায় গ্যাস কর্তৃক সম্পাদিত মোট কাজ এবং গ্যাসের সর্বোচ্চ তাপমাত্রা নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>##PRESET:carnot-cycle[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 41)।</t>
+          <t>$P-V$ লেখচিত্রের ট্রাপিজিয়ামের ক্ষেত্রফল: $W = \frac{P_0 + 2P_0}{2}(2V_0 - V_0) = \frac{3P_0}{2} V_0 = 1.5 P_0 V_0$। সরলরেখার সমীকরণ: $P - P_0 = \frac{2P_0 - P_0}{2V_0 - V_0}(V - V_0) \implies P = \frac{P_0}{V_0} V$। তাপমাত্রা $T = \frac{PV}{nR} = \frac{P_0}{n R V_0} V^2$ (যদি মূলবিন্দুগামী হয়) অথবা ট্রাপিজিয়াম সংযোগকারী রেখা অনুযায়ী মধ্যবিন্দুতে $T_{\max} = 2.25 T_0$।</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 41</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>সম্পাদিত কাজ $W = 1.5 P_0 V_0$, সর্বোচ্চ তাপমাত্রা $T_{\max} = \frac{9 P_0 V_0}{4 n R} = 2.25 T_0$</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5800,12 +5512,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>বরফ গলন ও তাপমাত্রা বৃদ্ধিতে এন্ট্রপি (সমস্যা 42)</t>
+          <t>উন্নত তাপগতীয় সংশ্লেষণ ও তাত্ত্বিক বিশ্লেষণ (Advanced Thermodynamics)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -5813,25 +5525,25 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>[সমস্যা 42: বরফ গলন ও তাপমাত্রা বৃদ্ধিতে এন্ট্রপি]
-$0^\circ\text{C}$ তাপমাত্রার $20\text{ g}$ বরফকে $50^\circ\text{C}$ তাপমাত্রার পানিতে রূপান্তরিত করা হলো। এই সামগ্রিক প্রক্রিয়ায় মোট এন্ট্রপির পরিবর্তন ($\Delta S$) কত জুল/কেলভিন? ($L_f = 3.36 \times 10^5\text{ J/kg}, s = 4200\text{ J/(kg}\cdot\text{K)}$)</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2.5,h=3.5][size:small]##
+একটি তাপ কুপরিবাহী পাত্রের রুদ্ধতাপীয় প্রাচীরের মাঝে একটি ছিদ্র দিয়ে $1.0\text{ মোল}$ একপরমাণুক গ্যাস ($\gamma = 5/3$) এবং $1.0\text{ মোল}$ দ্বিপরমাণুক গ্যাস ($\gamma = 7/5$) মিশ্রিত হলো। মিশ্রণের কার্যকর $\gamma_{	ext{mix}}$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2.5,h=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 42)।</t>
+          <t>$C_{v1} = 1.5 R, C_{v2} = 2.5 R$। মিশ্রণের মোলার তাপধারণ ক্ষমতা $C_{v,\text{mix}} = \frac{n_1 C_{v1} + n_2 C_{v2}}{n_1 + n_2} = \frac{1(1.5R) + 1(2.5R)}{2} = \frac{4R}{2} = 2.0 R$। $C_{p,\text{mix}} = C_{v,\text{mix}} + R = 3.0 R$। অতএব $\gamma_{\text{mix}} = \frac{C_{p,\text{mix}}}{C_{v,\text{mix}}} = \frac{3.0R}{2.0R} = 1.50$।</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 42</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>কার্যকর $\gamma_{\text{mix}} = 1.50$</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5851,44 +5563,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>রূদ্ধতাপীয় প্রসারণ ও কাজের হিসাব (সমস্যা 43)</t>
+          <t>উন্নত তাপগতীয় সংশ্লেষণ ও তাত্ত্বিক বিশ্লেষণ (Advanced Thermodynamics)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>##PRESET:heat-engine[size:medium]##
-[সমস্যা 43: রূদ্ধতাপীয় প্রসারণ ও কাজের হিসাব]
-##PRESET:heat-engine[size:medium]##
-$1\text{ mol}$ হিলিয়াম গ্যাস ($C_v = 1.5R$) প্রারম্ভিক তাপমাত্রা $T_1 = 400\text{ K}$ হতে রূদ্ধতাপীয় প্রক্রিয়ায় প্রসারিত হয়ে তাপমাত্রা $T_2 = 700\text{ K}$-এ নেমে এলো। গ্যাস কর্তৃক সম্পাদিত কাজের মান $W = n C_v(T_1 - T_2)$ কত জুল? ($R = 8.314\text{ J/(mol}\cdot\text{K)}$)</t>
+          <t>##GEO:circle[r=3][size:small]##
+একটি বেলুনে $10^5\text{ Pa}$ চাপে এবং $300\text{ K}$ তাপমাত্রায় $10\text{ m}^3$ হিলিয়াম গ্যাস রয়েছে। চারপাশের বায়ুমণ্ডলে হঠাৎ বেলুনটি ফেটে গেলে এই মুক্ত প্রসারণের পর হিলিয়াম গ্যাসটির তাপমাত্রা এবং এন্ট্রপির পরিবর্তন তাৎক্ষণিকভাবে কী হবে?</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>##PRESET:heat-engine[size:medium]##</t>
+          <t>##GEO:circle[r=3][size:small]##</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 43)।</t>
+          <t>আদর্শ গ্যাসের ক্ষেত্রে মুক্ত প্রসারণে কোনো কাজ হয় না ($W = 0$) এবং তাপ আদান-প্রদান ঘটে না ($Q = 0$)। ফলে $\Delta U = 0 \implies \Delta T = 0$, অর্থাৎ তাপমাত্রা $300\text{ K}$-এই স্থির থাকবে। তবে মুক্ত প্রসারণ অপরিবর্তনীয় হওয়ায় এন্ট্রপি নিশ্চিতভাবে বৃদ্ধি পাবে।</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 43</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>মুক্ত প্রসারণের পর তাৎক্ষণিক তাপমাত্রা প্রায় অপরিবর্তিত থাকবে ($300\text{ K}$), কিন্তু এন্ট্রপি বৃদ্ধি পাবে $\Delta S &gt; 0$</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5908,12 +5614,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>রেফ্রিজারেটরের কার্যসম্পাদন গুণক (COP) (সমস্যা 44)</t>
+          <t>উন্নত তাপগতীয় সংশ্লেষণ ও তাত্ত্বিক বিশ্লেষণ (Advanced Thermodynamics)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -5921,25 +5627,25 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[সমস্যা 44: রেফ্রিজারেটরের কার্যসম্পাদন গুণক (COP)]
-একটি আদর্শ রেফ্রিজারেটর $T_2 = -6^\circ\text{C}$ তাপমাত্রা হতে তাপ শোষণ করে $T_1 = 27^\circ\text{C}$ তাপমাত্রার বায়ুমণ্ডলে তাপ বর্জন করে। রেফ্রিজারেটরটির কার্যসম্পাদন সহগ বা গুণক ($COP = \frac{T_2}{T_1 - T_2}$) কত?</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি তাপ ইঞ্জিন চক্রের দুটি রুদ্ধতাপীয় রেখা এবং দুটি সমআয়তন রেখা দ্বারা গঠিত (Stirling / Otto type cycle)। এই চক্রের কর্মদক্ষতার সমীকরণ প্রতিপাদন কর।</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 44)।</t>
+          <t>সমআয়তন উত্তাপনে গৃহীত তাপ $Q_1 = n C_v (T_3 - T_2)$ এবং সমআয়তন শীতলীকরণে বর্জিত তাপ $Q_2 = n C_v (T_4 - T_1)$। রুদ্ধতাপীয় সম্পর্কের মাধ্যমে তাপমাত্রা অনুপাত প্রতিস্থাপন করে প্রমাণ করা যায় $\eta = 1 - \frac{Q_2}{Q_1} = 1 - \frac{T_1}{T_2} = 1 - \frac{1}{r^{\gamma-1}}$।</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 44</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>দক্ষতা $\eta = 1 - \left(\frac{V_2}{V_1}\right)^{\gamma-1} = 1 - \frac{1}{r^{\gamma-1}}$</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5959,38 +5665,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>সমোষ্ণ প্রক্রিয়ায় কৃতকাজ ও তাপ (সমস্যা 45)</t>
+          <t>উন্নত তাপগতীয় সংশ্লেষণ ও তাত্ত্বিক বিশ্লেষণ (Advanced Thermodynamics)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[সমস্যা 45: সমোষ্ণ প্রক্রিয়ায় কৃতকাজ ও তাপ]
-$V_1 = 1.0\text{ L}$ আয়তনের একটি আদর্শ গ্যাসকে স্থির তাপমাত্রা $T = 800\text{ K}$-এ সমোষ্ণ প্রক্রিয়ায় প্রসারিত করে আয়তন $V_2 = 1.0\text{ L}$ করা হলো। গ্যাসে প্রদত্ত তাপশক্তি ও কৃতকাজ $W = nRT \ln(V_2/V_1)$ কত? ($n = 1\text{ mol}$)</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি $2.0\text{ kW}$ বৈদ্যুতিক হিটার দ্বারা একটি সুষম তাপীয় অন্তরিত ঘরের তাপমাত্রা $15^\circ\text{C}$ হতে $25^\circ\text{C}$-এ উন্নীত করতে $15\text{ মিনিট}$ সময় লাগে। ঘরের বাতাসের মোট ভর $m$ কত কেজি? (বাতাসের $C_v = 718\text{ J/kg}\cdot\text{K}$)।</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 45)।</t>
+          <t>সরবরাহকৃত মোট তাপ শক্তি $Q = P \times t = 2000\text{ W} \times (15 \times 60\text{ s}) = 2000 \times 900 = 1.8 \times 10^6\text{ J}$। তাপমাত্রা বৃদ্ধি $\Delta T = 25 - 15 = 10\text{ K}$। $Q = m C_v \Delta T \implies m = \frac{Q}{C_v \Delta T} = \frac{1.8 \times 10^6}{718 \times 10} = \frac{1.8 \times 10^5}{718} \approx 250.7\text{ kg}$।</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 45</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>বাতাসের ভর $m = 250.7\text{ kg}$</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6010,12 +5716,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>পানি বাষ্পীভবনে এন্ট্রপি বৃদ্ধি (সমস্যা 46)</t>
+          <t>উন্নত তাপগতীয় সংশ্লেষণ ও তাত্ত্বিক বিশ্লেষণ (Advanced Thermodynamics)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -6023,25 +5729,25 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[সমস্যা 46: পানি বাষ্পীভবনে এন্ট্রপি বৃদ্ধি]
-$100^\circ\text{C}$ তাপমাত্রার $1000\text{ g}$ পানিকে ফুটন্ত অবস্থায় সম-তাপমাত্রার বাষ্পে পরিণত করা হলো। এই প্রক্রিয়ায় এন্ট্রপির পরিবর্তন কত? (বাষ্পীভবনের সুপ্ততাপ $L_v = 2.26 \times 10^6\text{ J/kg}$)</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি আদর্শ গ্যাসের পলিট্রপিক প্রক্রিয়ার (Polytropic process) সাধারণ সমীকরণ $P V^n = 	ext{ধ্রুবক}$। এই প্রক্রিয়ায় গ্যাসের মোলার তাপধারণ ক্ষমতা $C = C_v + rac{R}{1 - n}$ প্রমাণ কর। $n = \gamma$ হলে $C$ কত?</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 46)।</t>
+          <t>১ম সূত্র: $dQ = dU + dW = n C_v dT + P dV$। পলিট্রপিক প্রক্রিয়ায় কাজ $W = \frac{n R \Delta T}{1 - n} \implies dW = \frac{nR dT}{1 - n}$। ফলে $dQ = n C_v dT + \frac{nR dT}{1 - n} = n\left(C_v + \frac{R}{1 - n}\right)dT$। মোলার তাপধারণ ক্ষমতা $C = \frac{dQ}{n dT} = C_v + \frac{R}{1 - n}$। $n = \gamma$ হলে $C = C_v + \frac{R}{1 - \gamma} = C_v - C_v = 0$।</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 46</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>$C = C_v + \frac{R}{1 - n}$, রুদ্ধতাপীয় প্রক্রিয়ায় ($n = \gamma$) $C = 0$</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6061,38 +5767,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম সূত্র ও অভ্যন্তরীণ শক্তি (সমস্যা 47)</t>
+          <t>উন্নত তাপগতীয় সংশ্লেষণ ও তাত্ত্বিক বিশ্লেষণ (Advanced Thermodynamics)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[সমস্যা 47: তাপগতিবিদ্যার ১ম সূত্র ও অভ্যন্তরীণ শক্তি]
-একটি আবদ্ধ গ্যাস ব্যবস্থায় বাইরে হতে $\Delta Q = 1250\text{ J}$ তাপশক্তি সরবরাহ করা হলো এবং ব্যবস্থাটি সম্প্রসারিত হয়ে $\Delta W = 500\text{ J}$ কাজ সম্পাদন করল। ব্যবস্থার অভ্যন্তরীণ শক্তির পরিবর্তন $\Delta U = \Delta Q - \Delta W$ কত?</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2.5,h=4][size:small]##
+কোনো একদিন বায়ুমণ্ডলীয় চাপে $0^\circ\text{C}$ তাপমাত্রার $500\text{ g}$ বরফকে গলিয়ে বাষ্পে পরিণত করা পর্যন্ত মোট শোষিত তাপ এবং এন্ট্রপির মোট পরিবর্তন নির্ণয় কর। ($L_f = 3.36 	imes 10^5\text{ J/kg}, c_w = 4200\text{ J/kg}\cdot\text{K}, L_v = 2.26 	imes 10^6\text{ J/kg}$)।</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 47)।</t>
+          <t>১ম ধাপ (গলন): $Q_1 = 0.5 \times 3.36 \times 10^5 = 168000\text{ J}$, $\Delta S_1 = \frac{168000}{273.15} \approx 615.05\text{ J/K}$। ২য় ধাপ ($0 \to 100^\circ\text{C}$ পানি): $Q_2 = 0.5 \times 4200 \times 100 = 210000\text{ J}$, $\Delta S_2 = 0.5(4200)\ln(373.15/273.15) \approx 655.08\text{ J/K}$। ৩য় ধাপ (বাষ্পীভবন): $Q_3 = 0.5 \times 2.26 \times 10^6 = 1130000\text{ J}$, $\Delta S_3 = \frac{1130000}{373.15} \approx 3028.27\text{ J/K}$। মোট তাপ $Q = 168 + 210 + 1130 = 1508\text{ kJ}$। মোট এন্ট্রপি $\Delta S = 615.05 + 655.08 + 3028.27 = 4298.4\text{ J/K}$।</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 47</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>মোট তাপ $Q_{\text{total}} = 1.508 \times 10^6\text{ J} = 1508.0\text{ kJ}$, মোট এন্ট্রপি পরিবর্তন $\Delta S = 4300.2\text{ J/K}$</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6112,12 +5818,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>দ্বি-পরমাণুক গ্যাসের গামা ও রূদ্ধতাপীয় সমীকরণ (সমস্যা 48)</t>
+          <t>উন্নত তাপগতীয় সংশ্লেষণ ও তাত্ত্বিক বিশ্লেষণ (Advanced Thermodynamics)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -6125,25 +5831,25 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[সমস্যা 48: দ্বি-পরমাণুক গ্যাসের গামা ও রূদ্ধতাপীয় সমীকরণ]
-একটি দ্বি-পরমাণুক গ্যাসের জন্য $\gamma = 1.4$। গ্যাসটির প্রারম্ভিক চাপ $P_1 = 1\text{ atm}$ এবং আয়তন $V_1$ হতে রূদ্ধতাপীয় প্রক্রিয়ায় আয়তন সংকুচিত করে এক-চতুর্থাংশ ($V_2 = V_1 / 4$) করা হলে চূড়ান্ত চাপ $P_2 = P_1 (V_1/V_2)^\gamma$ কত অ্যাটমস্ফিয়ার হবে?</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##
+একটি আদর্শ গ্যাসকে সমচাপ প্রক্রিয়ায় এমনভাবে প্রসারিত করা হলো যাতে আয়তন দ্বিগুণ হয়। এরপর রুদ্ধতাপীয় প্রক্রিয়ায় আদি তাপমাত্রায় ফিরিয়ে আনা হলো। অন্তিম আয়তন কত হবে?</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 48)।</t>
+          <t>সমচাপে আয়তন দ্বিগুণ হওয়ায় তাপমাত্রা দ্বিগুণ হয়: $T_1 = 2T_0, V_1 = 2V_0$। এরপর রুদ্ধতাপীয় প্রসারণে তাপমাত্রা $2T_0$ হতে কমে পুনরায় $T_0$ হয়: $T_1 V_1^{\gamma-1} = T_0 V_f^{\gamma-1} \implies (2T_0)(2V_0)^{\gamma-1} = T_0 V_f^{\gamma-1} \implies V_f^{\gamma-1} = 2 \times (2V_0)^{\gamma-1} = 2^\gamma V_0^{\gamma-1} \implies V_f = 2^{\frac{\gamma}{\gamma-1}} V_0$।</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 48</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>অন্তিম আয়তন $V_f = 2^{\frac{\gamma}{\gamma-1}} V_0$</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6163,38 +5869,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>কার্নো ইঞ্জিনের গ্রাহকের তাপমাত্রা পরিবর্তন (সমস্যা 49)</t>
+          <t>উন্নত তাপগতীয় সংশ্লেষণ ও তাত্ত্বিক বিশ্লেষণ (Advanced Thermodynamics)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[সমস্যা 49: কার্নো ইঞ্জিনের গ্রাহকের তাপমাত্রা পরিবর্তন]
-একটি কার্নো ইঞ্জিনের বর্তমান দক্ষতা $40\%$। তাপগ্রাহকের তাপমাত্রা $90\text{ K}$ হ্রাস করলে ইঞ্জিনের নতুন দক্ষতা কত বৃদ্ধি পাবে, যদি উৎসের তাপমাত্রা $T_1 = 600\text{ K}$ স্থির থাকে?</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2.5,h=3][size:small]##
+একটি তাপীয় অন্তরিত পাত্রে দুটি প্রকোষ্ঠ একটি কপাটিকা দ্বারা বিভক্ত। এক প্রকোষ্ঠে $T_1$ তাপমাত্রায় $n_1$ মোল এবং অপর প্রকোষ্ঠে $T_2$ তাপমাত্রায় $n_2$ মোল একই আদর্শ গ্যাস রয়েছে। কপাটিকা খুলে দিলে মিশ্রণের চূড়ান্ত ভারসাম্য তাপমাত্রা কত হবে?</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2.5,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 49)।</t>
+          <t>অন্তরিত পাত্রে মোট অভ্যন্তরীণ শক্তি সংরক্ষিত থাকে: $U_{\text{initial}} = U_{\text{final}} \implies n_1 C_v T_1 + n_2 C_v T_2 = (n_1 + n_2) C_v T_f \implies T_f = \frac{n_1 T_1 + n_2 T_2}{n_1 + n_2}$।</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 49</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>$T_f = \frac{n_1 T_1 + n_2 T_2}{n_1 + n_2}$</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6214,12 +5920,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>থার্মোমিটারের মৌলিক ব্যবধান ও পরম শূন্য (সমস্যা 50)</t>
+          <t>উন্নত তাপগতীয় সংশ্লেষণ ও তাত্ত্বিক বিশ্লেষণ (Advanced Thermodynamics)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -6227,25 +5933,25 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[সমস্যা 50: থার্মোমিটারের মৌলিক ব্যবধান ও পরম শূন্য]
-একটি ত্রুটিপূর্ণ থার্মোমিটার গলিত বরফে $6^\circ\text{C}$ এবং প্রমাণ চাপে বাষ্পে $91^\circ\text{C}$ পাঠ প্রদর্শন করে। থার্মোমিটারটি $50^\circ\text{C}$ পাঠ দিলে ফারেনহাইট স্কেলে এর সঠিক মান কত?</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+তাপগতিবিদ্যার ৩য় সূত্র (Third Law of Thermodynamics / Nernst Heat Theorem) বলতে কী বোঝায় এবং কেন পরম শূন্য তাপমাত্রায় ($0\text{ K}$) কোনো আদর্শ ক্রিস্টালের এন্ট্রপি শূন্য হয়?</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার ১ম ও ২য় সূত্রের গাণিতিক রূপ ও এন্ট্রপির সমীকরণ দ্বারা সমাধান (সমস্যা 50)।</t>
+          <t>তাপমাত্রা যখন পরম শূন্যের ($0\text{ K}$) দিকে ধাবিত হয় তখন সমস্ত আণবিক ও পারমাণবিক তাপীয় কম্পন স্তব্ধ হয়ে যায়। নিখুঁত স্ফটিকাকার জালির সমস্ত কণা একমাত্র ন্যূনতম শক্তি অবস্থায় (Ground state, $W = 1$) অবস্থান করে। বোল্টজম্যান সূত্রানুসারে এন্ট্রপি $S = k_B \ln(W) = k_B \ln(1) = 0$। এটিই তাপগতিবিদ্যার তৃতীয় সূত্র।</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>তাপগতিবিদ্যার সমাধান 50</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>পরম শূন্য তাপমাত্রায় বিশুদ্ধ নিখুঁত স্ফটিকের এন্ট্রপি শূন্য হয় ($S \to 0$ as $T \to 0\text{ K}$)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
